--- a/research/traditional_assets/database/data/philippines/philippines_coal_related_energy.xlsx
+++ b/research/traditional_assets/database/data/philippines/philippines_coal_related_energy.xlsx
@@ -1388,7 +1388,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1525,22 +1525,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1202935188499009</v>
+        <v>0.1200265350527762</v>
       </c>
       <c r="C2">
-        <v>2614.715887029195</v>
+        <v>2593.002946487428</v>
       </c>
       <c r="D2">
-        <v>2269.015887029195</v>
+        <v>2273.497946487428</v>
       </c>
       <c r="E2">
-        <v>-65.3</v>
+        <v>-39.105</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>26.195</v>
       </c>
       <c r="G2">
         <v>345.7</v>
@@ -1561,28 +1561,28 @@
         <v>528.38</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.3176085</v>
       </c>
       <c r="N2">
-        <v>528.38</v>
+        <v>527.0623915</v>
       </c>
       <c r="O2">
-        <v>132.095</v>
+        <v>131.765597875</v>
       </c>
       <c r="P2">
-        <v>396.285</v>
+        <v>395.296793625</v>
       </c>
       <c r="Q2">
-        <v>397.405</v>
+        <v>396.416793625</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1202935188499009</v>
+        <v>0.1208578636896729</v>
       </c>
       <c r="T2">
-        <v>1.083971466858168</v>
+        <v>1.092183371910124</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>401.0144136137556</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1607,22 +1607,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1200265350527762</v>
+        <v>0.1197595512556514</v>
       </c>
       <c r="C3">
-        <v>2593.002946487428</v>
+        <v>2571.30774810234</v>
       </c>
       <c r="D3">
-        <v>2273.497946487428</v>
+        <v>2277.99774810234</v>
       </c>
       <c r="E3">
-        <v>-39.105</v>
+        <v>-12.91</v>
       </c>
       <c r="F3">
-        <v>26.195</v>
+        <v>52.39</v>
       </c>
       <c r="G3">
         <v>345.7</v>
@@ -1643,28 +1643,28 @@
         <v>528.38</v>
       </c>
       <c r="M3">
-        <v>1.3176085</v>
+        <v>2.635217</v>
       </c>
       <c r="N3">
-        <v>527.0623915</v>
+        <v>525.744783</v>
       </c>
       <c r="O3">
-        <v>131.765597875</v>
+        <v>131.43619575</v>
       </c>
       <c r="P3">
-        <v>395.296793625</v>
+        <v>394.30858725</v>
       </c>
       <c r="Q3">
-        <v>396.416793625</v>
+        <v>395.42858725</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1208578636896729</v>
+        <v>0.1214337257710729</v>
       </c>
       <c r="T3">
-        <v>1.092183371910124</v>
+        <v>1.100562866861099</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>401.0144136137556</v>
+        <v>200.5072068068778</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1689,22 +1689,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1197595512556514</v>
+        <v>0.1194925674585267</v>
       </c>
       <c r="C4">
-        <v>2571.30774810234</v>
+        <v>2549.630397430896</v>
       </c>
       <c r="D4">
-        <v>2277.99774810234</v>
+        <v>2282.515397430896</v>
       </c>
       <c r="E4">
-        <v>-12.91</v>
+        <v>13.285</v>
       </c>
       <c r="F4">
-        <v>52.39</v>
+        <v>78.58499999999999</v>
       </c>
       <c r="G4">
         <v>345.7</v>
@@ -1725,28 +1725,28 @@
         <v>528.38</v>
       </c>
       <c r="M4">
-        <v>2.635217</v>
+        <v>3.952825499999999</v>
       </c>
       <c r="N4">
-        <v>525.744783</v>
+        <v>524.4271745</v>
       </c>
       <c r="O4">
-        <v>131.43619575</v>
+        <v>131.106793625</v>
       </c>
       <c r="P4">
-        <v>394.30858725</v>
+        <v>393.320380875</v>
       </c>
       <c r="Q4">
-        <v>395.42858725</v>
+        <v>394.440380875</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1214337257710729</v>
+        <v>0.1220214612974502</v>
       </c>
       <c r="T4">
-        <v>1.100562866861099</v>
+        <v>1.109115134903847</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1763,7 +1763,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>200.5072068068778</v>
+        <v>133.6714712045852</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1771,22 +1771,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1194925674585267</v>
+        <v>0.1192255836614019</v>
       </c>
       <c r="C5">
-        <v>2549.630397430896</v>
+        <v>2527.971000869071</v>
       </c>
       <c r="D5">
-        <v>2282.515397430896</v>
+        <v>2287.051000869071</v>
       </c>
       <c r="E5">
-        <v>13.285</v>
+        <v>39.48</v>
       </c>
       <c r="F5">
-        <v>78.58499999999999</v>
+        <v>104.78</v>
       </c>
       <c r="G5">
         <v>345.7</v>
@@ -1807,28 +1807,28 @@
         <v>528.38</v>
       </c>
       <c r="M5">
-        <v>3.952825499999999</v>
+        <v>5.270434</v>
       </c>
       <c r="N5">
-        <v>524.4271745</v>
+        <v>523.109566</v>
       </c>
       <c r="O5">
-        <v>131.106793625</v>
+        <v>130.7773915</v>
       </c>
       <c r="P5">
-        <v>393.320380875</v>
+        <v>392.3321745</v>
       </c>
       <c r="Q5">
-        <v>394.440380875</v>
+        <v>393.4521745</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1220214612974502</v>
+        <v>0.1226214413139603</v>
       </c>
       <c r="T5">
-        <v>1.109115134903847</v>
+        <v>1.117845575197486</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1845,7 +1845,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>133.6714712045852</v>
+        <v>100.2536034034389</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1853,22 +1853,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1192255836614019</v>
+        <v>0.1189585998642772</v>
       </c>
       <c r="C6">
-        <v>2527.971000869071</v>
+        <v>2506.329665660207</v>
       </c>
       <c r="D6">
-        <v>2287.051000869071</v>
+        <v>2291.604665660207</v>
       </c>
       <c r="E6">
-        <v>39.48</v>
+        <v>65.675</v>
       </c>
       <c r="F6">
-        <v>104.78</v>
+        <v>130.975</v>
       </c>
       <c r="G6">
         <v>345.7</v>
@@ -1889,28 +1889,28 @@
         <v>528.38</v>
       </c>
       <c r="M6">
-        <v>5.270434</v>
+        <v>6.588042499999999</v>
       </c>
       <c r="N6">
-        <v>523.109566</v>
+        <v>521.7919575</v>
       </c>
       <c r="O6">
-        <v>130.7773915</v>
+        <v>130.447989375</v>
       </c>
       <c r="P6">
-        <v>392.3321745</v>
+        <v>391.3439681249999</v>
       </c>
       <c r="Q6">
-        <v>393.4521745</v>
+        <v>392.463968125</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1226214413139603</v>
+        <v>0.1232340524887128</v>
       </c>
       <c r="T6">
-        <v>1.117845575197486</v>
+        <v>1.126759814234148</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1927,7 +1927,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>100.2536034034389</v>
+        <v>80.20288272275111</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1935,22 +1935,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1189585998642772</v>
+        <v>0.1186916160671524</v>
       </c>
       <c r="C7">
-        <v>2506.329665660207</v>
+        <v>2484.706499903461</v>
       </c>
       <c r="D7">
-        <v>2291.604665660207</v>
+        <v>2296.176499903462</v>
       </c>
       <c r="E7">
-        <v>65.675</v>
+        <v>91.87000000000002</v>
       </c>
       <c r="F7">
-        <v>130.975</v>
+        <v>157.17</v>
       </c>
       <c r="G7">
         <v>345.7</v>
@@ -1971,28 +1971,28 @@
         <v>528.38</v>
       </c>
       <c r="M7">
-        <v>6.588042499999999</v>
+        <v>7.905651000000001</v>
       </c>
       <c r="N7">
-        <v>521.7919575</v>
+        <v>520.474349</v>
       </c>
       <c r="O7">
-        <v>130.447989375</v>
+        <v>130.11858725</v>
       </c>
       <c r="P7">
-        <v>391.3439681249999</v>
+        <v>390.3557617499999</v>
       </c>
       <c r="Q7">
-        <v>392.463968125</v>
+        <v>391.4757617499999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1232340524887128</v>
+        <v>0.1238596979437792</v>
       </c>
       <c r="T7">
-        <v>1.126759814234148</v>
+        <v>1.135863717931165</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>80.20288272275111</v>
+        <v>66.83573560229257</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2017,22 +2017,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1186916160671524</v>
+        <v>0.1184246322700277</v>
       </c>
       <c r="C8">
-        <v>2484.706499903461</v>
+        <v>2463.101612562366</v>
       </c>
       <c r="D8">
-        <v>2296.176499903462</v>
+        <v>2300.766612562366</v>
       </c>
       <c r="E8">
-        <v>91.86999999999999</v>
+        <v>118.065</v>
       </c>
       <c r="F8">
-        <v>157.17</v>
+        <v>183.365</v>
       </c>
       <c r="G8">
         <v>345.7</v>
@@ -2053,28 +2053,28 @@
         <v>528.38</v>
       </c>
       <c r="M8">
-        <v>7.905650999999999</v>
+        <v>9.223259499999999</v>
       </c>
       <c r="N8">
-        <v>520.474349</v>
+        <v>519.1567405</v>
       </c>
       <c r="O8">
-        <v>130.11858725</v>
+        <v>129.789185125</v>
       </c>
       <c r="P8">
-        <v>390.3557617499999</v>
+        <v>389.3675553749999</v>
       </c>
       <c r="Q8">
-        <v>391.4757617499999</v>
+        <v>390.4875553749999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1238596979437792</v>
+        <v>0.1244987981398147</v>
       </c>
       <c r="T8">
-        <v>1.135863717931165</v>
+        <v>1.145163404503387</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2091,7 +2091,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>66.83573560229259</v>
+        <v>57.28777337339365</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2099,22 +2099,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1184246322700276</v>
+        <v>0.1181576484729029</v>
       </c>
       <c r="C9">
-        <v>2463.101612562366</v>
+        <v>2441.515113473477</v>
       </c>
       <c r="D9">
-        <v>2300.766612562366</v>
+        <v>2305.375113473477</v>
       </c>
       <c r="E9">
-        <v>118.065</v>
+        <v>144.26</v>
       </c>
       <c r="F9">
-        <v>183.365</v>
+        <v>209.56</v>
       </c>
       <c r="G9">
         <v>345.7</v>
@@ -2135,28 +2135,28 @@
         <v>528.38</v>
       </c>
       <c r="M9">
-        <v>9.223259499999999</v>
+        <v>10.540868</v>
       </c>
       <c r="N9">
-        <v>519.1567405</v>
+        <v>517.8391319999999</v>
       </c>
       <c r="O9">
-        <v>129.789185125</v>
+        <v>129.459783</v>
       </c>
       <c r="P9">
-        <v>389.3675553749999</v>
+        <v>388.3793489999999</v>
       </c>
       <c r="Q9">
-        <v>390.4875553749999</v>
+        <v>389.4993489999999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1244987981398147</v>
+        <v>0.1251517918183727</v>
       </c>
       <c r="T9">
-        <v>1.145163404503387</v>
+        <v>1.154665258175005</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>57.28777337339365</v>
+        <v>50.12680170171944</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2181,22 +2181,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1181576484729029</v>
+        <v>0.1178906646757781</v>
       </c>
       <c r="C10">
-        <v>2441.515113473477</v>
+        <v>2419.947113355143</v>
       </c>
       <c r="D10">
-        <v>2305.375113473477</v>
+        <v>2310.002113355143</v>
       </c>
       <c r="E10">
-        <v>144.26</v>
+        <v>170.455</v>
       </c>
       <c r="F10">
-        <v>209.56</v>
+        <v>235.755</v>
       </c>
       <c r="G10">
         <v>345.7</v>
@@ -2217,28 +2217,28 @@
         <v>528.38</v>
       </c>
       <c r="M10">
-        <v>10.540868</v>
+        <v>11.8584765</v>
       </c>
       <c r="N10">
-        <v>517.8391319999999</v>
+        <v>516.5215234999999</v>
       </c>
       <c r="O10">
-        <v>129.459783</v>
+        <v>129.130380875</v>
       </c>
       <c r="P10">
-        <v>388.3793489999999</v>
+        <v>387.3911426249999</v>
       </c>
       <c r="Q10">
-        <v>389.4993489999999</v>
+        <v>388.5111426249999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1251517918183727</v>
+        <v>0.1258191370063496</v>
       </c>
       <c r="T10">
-        <v>1.154665258175005</v>
+        <v>1.16437594379545</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>50.12680170171944</v>
+        <v>44.55715706819506</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1178906646757781</v>
+        <v>0.1176236808786534</v>
       </c>
       <c r="C11">
-        <v>2419.947113355143</v>
+        <v>2398.397723816365</v>
       </c>
       <c r="D11">
-        <v>2310.002113355143</v>
+        <v>2314.647723816365</v>
       </c>
       <c r="E11">
-        <v>170.455</v>
+        <v>196.65</v>
       </c>
       <c r="F11">
-        <v>235.755</v>
+        <v>261.95</v>
       </c>
       <c r="G11">
         <v>345.7</v>
@@ -2299,28 +2299,28 @@
         <v>528.38</v>
       </c>
       <c r="M11">
-        <v>11.8584765</v>
+        <v>13.176085</v>
       </c>
       <c r="N11">
-        <v>516.5215234999999</v>
+        <v>515.2039150000001</v>
       </c>
       <c r="O11">
-        <v>129.130380875</v>
+        <v>128.80097875</v>
       </c>
       <c r="P11">
-        <v>387.3911426249999</v>
+        <v>386.40293625</v>
       </c>
       <c r="Q11">
-        <v>388.5111426249999</v>
+        <v>387.52293625</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1258191370063496</v>
+        <v>0.1265013120873927</v>
       </c>
       <c r="T11">
-        <v>1.16437594379545</v>
+        <v>1.174302422429682</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2337,7 +2337,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>44.55715706819506</v>
+        <v>40.10144136137556</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2345,22 +2345,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1176236808786534</v>
+        <v>0.1173566970815287</v>
       </c>
       <c r="C12">
-        <v>2398.397723816365</v>
+        <v>2376.867057365779</v>
       </c>
       <c r="D12">
-        <v>2314.647723816365</v>
+        <v>2319.312057365779</v>
       </c>
       <c r="E12">
-        <v>196.65</v>
+        <v>222.845</v>
       </c>
       <c r="F12">
-        <v>261.95</v>
+        <v>288.145</v>
       </c>
       <c r="G12">
         <v>345.7</v>
@@ -2381,28 +2381,28 @@
         <v>528.38</v>
       </c>
       <c r="M12">
-        <v>13.176085</v>
+        <v>14.4936935</v>
       </c>
       <c r="N12">
-        <v>515.2039150000001</v>
+        <v>513.8863065</v>
       </c>
       <c r="O12">
-        <v>128.80097875</v>
+        <v>128.471576625</v>
       </c>
       <c r="P12">
-        <v>386.40293625</v>
+        <v>385.414729875</v>
       </c>
       <c r="Q12">
-        <v>387.52293625</v>
+        <v>386.534729875</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1265013120873927</v>
+        <v>0.1271988169455378</v>
       </c>
       <c r="T12">
-        <v>1.174302422429682</v>
+        <v>1.184451967999515</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2419,7 +2419,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>40.10144136137556</v>
+        <v>36.45585578306869</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2427,22 +2427,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1173566970815287</v>
+        <v>0.1170897132844039</v>
       </c>
       <c r="C13">
-        <v>2376.867057365779</v>
+        <v>2355.35522742073</v>
       </c>
       <c r="D13">
-        <v>2319.312057365779</v>
+        <v>2323.99522742073</v>
       </c>
       <c r="E13">
-        <v>222.845</v>
+        <v>249.04</v>
       </c>
       <c r="F13">
-        <v>288.145</v>
+        <v>314.34</v>
       </c>
       <c r="G13">
         <v>345.7</v>
@@ -2463,28 +2463,28 @@
         <v>528.38</v>
       </c>
       <c r="M13">
-        <v>14.4936935</v>
+        <v>15.811302</v>
       </c>
       <c r="N13">
-        <v>513.8863065</v>
+        <v>512.568698</v>
       </c>
       <c r="O13">
-        <v>128.471576625</v>
+        <v>128.1421745</v>
       </c>
       <c r="P13">
-        <v>385.414729875</v>
+        <v>384.4265235</v>
       </c>
       <c r="Q13">
-        <v>386.534729875</v>
+        <v>385.5465235</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1271988169455378</v>
+        <v>0.1279121741868226</v>
       </c>
       <c r="T13">
-        <v>1.184451967999515</v>
+        <v>1.194832185059572</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2501,7 +2501,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>36.45585578306869</v>
+        <v>33.4178678011463</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2509,22 +2509,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1170897132844039</v>
+        <v>0.1168227294872792</v>
       </c>
       <c r="C14">
-        <v>2355.35522742073</v>
+        <v>2333.862348316468</v>
       </c>
       <c r="D14">
-        <v>2323.99522742073</v>
+        <v>2328.697348316468</v>
       </c>
       <c r="E14">
-        <v>249.04</v>
+        <v>275.235</v>
       </c>
       <c r="F14">
-        <v>314.34</v>
+        <v>340.535</v>
       </c>
       <c r="G14">
         <v>345.7</v>
@@ -2545,28 +2545,28 @@
         <v>528.38</v>
       </c>
       <c r="M14">
-        <v>15.811302</v>
+        <v>17.1289105</v>
       </c>
       <c r="N14">
-        <v>512.568698</v>
+        <v>511.2510895</v>
       </c>
       <c r="O14">
-        <v>128.1421745</v>
+        <v>127.812772375</v>
       </c>
       <c r="P14">
-        <v>384.4265235</v>
+        <v>383.438317125</v>
       </c>
       <c r="Q14">
-        <v>385.5465235</v>
+        <v>384.558317125</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1279121741868226</v>
+        <v>0.1286419304451485</v>
       </c>
       <c r="T14">
-        <v>1.194832185059572</v>
+        <v>1.20545102779917</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>33.4178678011463</v>
+        <v>30.8472625856735</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2591,22 +2591,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1168227294872792</v>
+        <v>0.1165557456901544</v>
       </c>
       <c r="C15">
-        <v>2333.862348316468</v>
+        <v>2312.388535315457</v>
       </c>
       <c r="D15">
-        <v>2328.697348316468</v>
+        <v>2333.418535315457</v>
       </c>
       <c r="E15">
-        <v>275.235</v>
+        <v>301.43</v>
       </c>
       <c r="F15">
-        <v>340.535</v>
+        <v>366.73</v>
       </c>
       <c r="G15">
         <v>345.7</v>
@@ -2627,28 +2627,28 @@
         <v>528.38</v>
       </c>
       <c r="M15">
-        <v>17.1289105</v>
+        <v>18.446519</v>
       </c>
       <c r="N15">
-        <v>511.2510895</v>
+        <v>509.933481</v>
       </c>
       <c r="O15">
-        <v>127.812772375</v>
+        <v>127.48337025</v>
       </c>
       <c r="P15">
-        <v>383.438317125</v>
+        <v>382.45011075</v>
       </c>
       <c r="Q15">
-        <v>384.558317125</v>
+        <v>383.57011075</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1286419304451485</v>
+        <v>0.1293886577792493</v>
       </c>
       <c r="T15">
-        <v>1.20545102779917</v>
+        <v>1.216316820369921</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2665,7 +2665,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>30.8472625856735</v>
+        <v>28.64388668669682</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2673,22 +2673,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1165557456901544</v>
+        <v>0.1162887618930297</v>
       </c>
       <c r="C16">
-        <v>2312.388535315457</v>
+        <v>2290.933904616786</v>
       </c>
       <c r="D16">
-        <v>2333.418535315457</v>
+        <v>2338.158904616786</v>
       </c>
       <c r="E16">
-        <v>301.43</v>
+        <v>327.6250000000001</v>
       </c>
       <c r="F16">
-        <v>366.73</v>
+        <v>392.9250000000001</v>
       </c>
       <c r="G16">
         <v>345.7</v>
@@ -2709,28 +2709,28 @@
         <v>528.38</v>
       </c>
       <c r="M16">
-        <v>18.446519</v>
+        <v>19.7641275</v>
       </c>
       <c r="N16">
-        <v>509.933481</v>
+        <v>508.6158725</v>
       </c>
       <c r="O16">
-        <v>127.48337025</v>
+        <v>127.153968125</v>
       </c>
       <c r="P16">
-        <v>382.45011075</v>
+        <v>381.461904375</v>
       </c>
       <c r="Q16">
-        <v>383.57011075</v>
+        <v>382.581904375</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1293886577792493</v>
+        <v>0.1301529551682702</v>
       </c>
       <c r="T16">
-        <v>1.216316820369921</v>
+        <v>1.22743827864822</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>28.64388668669682</v>
+        <v>26.73429424091703</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2755,22 +2755,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1162887618930297</v>
+        <v>0.1160217780959049</v>
       </c>
       <c r="C17">
-        <v>2290.933904616786</v>
+        <v>2269.498573365709</v>
       </c>
       <c r="D17">
-        <v>2338.158904616786</v>
+        <v>2342.918573365709</v>
       </c>
       <c r="E17">
-        <v>327.625</v>
+        <v>353.82</v>
       </c>
       <c r="F17">
-        <v>392.925</v>
+        <v>419.12</v>
       </c>
       <c r="G17">
         <v>345.7</v>
@@ -2791,28 +2791,28 @@
         <v>528.38</v>
       </c>
       <c r="M17">
-        <v>19.7641275</v>
+        <v>21.081736</v>
       </c>
       <c r="N17">
-        <v>508.6158725</v>
+        <v>507.298264</v>
       </c>
       <c r="O17">
-        <v>127.153968125</v>
+        <v>126.824566</v>
       </c>
       <c r="P17">
-        <v>381.461904375</v>
+        <v>380.473698</v>
       </c>
       <c r="Q17">
-        <v>382.581904375</v>
+        <v>381.593698</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1301529551682702</v>
+        <v>0.1309354501141725</v>
       </c>
       <c r="T17">
-        <v>1.22743827864822</v>
+        <v>1.238824533552192</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2829,7 +2829,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>26.73429424091703</v>
+        <v>25.06340085085972</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2837,22 +2837,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1160217780959049</v>
+        <v>0.1157547942987801</v>
       </c>
       <c r="C18">
-        <v>2269.498573365709</v>
+        <v>2248.082659663288</v>
       </c>
       <c r="D18">
-        <v>2342.918573365709</v>
+        <v>2347.697659663288</v>
       </c>
       <c r="E18">
-        <v>353.82</v>
+        <v>380.015</v>
       </c>
       <c r="F18">
-        <v>419.12</v>
+        <v>445.3150000000001</v>
       </c>
       <c r="G18">
         <v>345.7</v>
@@ -2873,28 +2873,28 @@
         <v>528.38</v>
       </c>
       <c r="M18">
-        <v>21.081736</v>
+        <v>22.3993445</v>
       </c>
       <c r="N18">
-        <v>507.298264</v>
+        <v>505.9806555</v>
       </c>
       <c r="O18">
-        <v>126.824566</v>
+        <v>126.495163875</v>
       </c>
       <c r="P18">
-        <v>380.473698</v>
+        <v>379.485491625</v>
       </c>
       <c r="Q18">
-        <v>381.593698</v>
+        <v>380.605491625</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1309354501141725</v>
+        <v>0.1317368003599761</v>
       </c>
       <c r="T18">
-        <v>1.238824533552192</v>
+        <v>1.250485156044212</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2911,7 +2911,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>25.06340085085972</v>
+        <v>23.58908315375032</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2919,22 +2919,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1157547942987801</v>
+        <v>0.1154878105016554</v>
       </c>
       <c r="C19">
-        <v>2248.082659663288</v>
+        <v>2226.686282576169</v>
       </c>
       <c r="D19">
-        <v>2347.697659663288</v>
+        <v>2352.496282576169</v>
       </c>
       <c r="E19">
-        <v>380.015</v>
+        <v>406.21</v>
       </c>
       <c r="F19">
-        <v>445.3150000000001</v>
+        <v>471.51</v>
       </c>
       <c r="G19">
         <v>345.7</v>
@@ -2955,28 +2955,28 @@
         <v>528.38</v>
       </c>
       <c r="M19">
-        <v>22.3993445</v>
+        <v>23.716953</v>
       </c>
       <c r="N19">
-        <v>505.9806555</v>
+        <v>504.663047</v>
       </c>
       <c r="O19">
-        <v>126.495163875</v>
+        <v>126.16576175</v>
       </c>
       <c r="P19">
-        <v>379.485491625</v>
+        <v>378.49728525</v>
       </c>
       <c r="Q19">
-        <v>380.605491625</v>
+        <v>379.61728525</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1317368003599761</v>
+        <v>0.1325576957337261</v>
       </c>
       <c r="T19">
-        <v>1.250485156044212</v>
+        <v>1.262430183962866</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2993,7 +2993,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>23.58908315375032</v>
+        <v>22.27857853409753</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3001,22 +3001,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1154878105016554</v>
+        <v>0.1152208267045306</v>
       </c>
       <c r="C20">
-        <v>2226.686282576168</v>
+        <v>2205.309562146463</v>
       </c>
       <c r="D20">
-        <v>2352.496282576169</v>
+        <v>2357.314562146463</v>
       </c>
       <c r="E20">
-        <v>406.21</v>
+        <v>432.405</v>
       </c>
       <c r="F20">
-        <v>471.51</v>
+        <v>497.705</v>
       </c>
       <c r="G20">
         <v>345.7</v>
@@ -3037,28 +3037,28 @@
         <v>528.38</v>
       </c>
       <c r="M20">
-        <v>23.716953</v>
+        <v>25.0345615</v>
       </c>
       <c r="N20">
-        <v>504.663047</v>
+        <v>503.3454385</v>
       </c>
       <c r="O20">
-        <v>126.16576175</v>
+        <v>125.836359625</v>
       </c>
       <c r="P20">
-        <v>378.49728525</v>
+        <v>377.509078875</v>
       </c>
       <c r="Q20">
-        <v>379.61728525</v>
+        <v>378.629078875</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1325576957337261</v>
+        <v>0.1333988601290502</v>
       </c>
       <c r="T20">
-        <v>1.262430183962866</v>
+        <v>1.274670150842476</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3075,7 +3075,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>22.27857853409753</v>
+        <v>21.10602176914503</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3083,22 +3083,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1152208267045306</v>
+        <v>0.1149538429074059</v>
       </c>
       <c r="C21">
-        <v>2205.309562146463</v>
+        <v>2183.952619401762</v>
       </c>
       <c r="D21">
-        <v>2357.314562146463</v>
+        <v>2362.152619401762</v>
       </c>
       <c r="E21">
-        <v>432.405</v>
+        <v>458.6</v>
       </c>
       <c r="F21">
-        <v>497.705</v>
+        <v>523.9</v>
       </c>
       <c r="G21">
         <v>345.7</v>
@@ -3119,28 +3119,28 @@
         <v>528.38</v>
       </c>
       <c r="M21">
-        <v>25.0345615</v>
+        <v>26.35217</v>
       </c>
       <c r="N21">
-        <v>503.3454385</v>
+        <v>502.02783</v>
       </c>
       <c r="O21">
-        <v>125.836359625</v>
+        <v>125.5069575</v>
       </c>
       <c r="P21">
-        <v>377.509078875</v>
+        <v>376.5208725</v>
       </c>
       <c r="Q21">
-        <v>378.629078875</v>
+        <v>377.6408725</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1333988601290502</v>
+        <v>0.1342610536342574</v>
       </c>
       <c r="T21">
-        <v>1.274670150842476</v>
+        <v>1.287216116894075</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3157,7 +3157,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>21.10602176914503</v>
+        <v>20.05072068068778</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3165,22 +3165,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1149538429074059</v>
+        <v>0.1146868591102811</v>
       </c>
       <c r="C22">
-        <v>2183.952619401762</v>
+        <v>2162.615576365267</v>
       </c>
       <c r="D22">
-        <v>2362.152619401762</v>
+        <v>2367.010576365267</v>
       </c>
       <c r="E22">
-        <v>458.6</v>
+        <v>484.795</v>
       </c>
       <c r="F22">
-        <v>523.9</v>
+        <v>550.095</v>
       </c>
       <c r="G22">
         <v>345.7</v>
@@ -3201,28 +3201,28 @@
         <v>528.38</v>
       </c>
       <c r="M22">
-        <v>26.35217</v>
+        <v>27.6697785</v>
       </c>
       <c r="N22">
-        <v>502.02783</v>
+        <v>500.7102215</v>
       </c>
       <c r="O22">
-        <v>125.5069575</v>
+        <v>125.177555375</v>
       </c>
       <c r="P22">
-        <v>376.5208725</v>
+        <v>375.532666125</v>
       </c>
       <c r="Q22">
-        <v>377.6408725</v>
+        <v>376.652666125</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1342610536342574</v>
+        <v>0.1351450748231407</v>
       </c>
       <c r="T22">
-        <v>1.287216116894075</v>
+        <v>1.300079702339385</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3239,7 +3239,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>20.05072068068778</v>
+        <v>19.09592445779788</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3247,22 +3247,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1146868591102811</v>
+        <v>0.1144198753131564</v>
       </c>
       <c r="C23">
-        <v>2162.615576365268</v>
+        <v>2141.298556066054</v>
       </c>
       <c r="D23">
-        <v>2367.010576365268</v>
+        <v>2371.888556066054</v>
       </c>
       <c r="E23">
-        <v>484.795</v>
+        <v>510.99</v>
       </c>
       <c r="F23">
-        <v>550.095</v>
+        <v>576.29</v>
       </c>
       <c r="G23">
         <v>345.7</v>
@@ -3283,28 +3283,28 @@
         <v>528.38</v>
       </c>
       <c r="M23">
-        <v>27.6697785</v>
+        <v>28.987387</v>
       </c>
       <c r="N23">
-        <v>500.7102215</v>
+        <v>499.392613</v>
       </c>
       <c r="O23">
-        <v>125.177555375</v>
+        <v>124.84815325</v>
       </c>
       <c r="P23">
-        <v>375.532666125</v>
+        <v>374.54445975</v>
       </c>
       <c r="Q23">
-        <v>376.652666125</v>
+        <v>375.66445975</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1351450748231407</v>
+        <v>0.1360517632219954</v>
       </c>
       <c r="T23">
-        <v>1.300079702339385</v>
+        <v>1.313273123308934</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3321,7 +3321,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>19.09592445779788</v>
+        <v>18.22792789153434</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1144198753131564</v>
+        <v>0.1141528915160316</v>
       </c>
       <c r="C24">
-        <v>2141.298556066054</v>
+        <v>2120.00168254945</v>
       </c>
       <c r="D24">
-        <v>2371.888556066054</v>
+        <v>2376.78668254945</v>
       </c>
       <c r="E24">
-        <v>510.99</v>
+        <v>537.1850000000001</v>
       </c>
       <c r="F24">
-        <v>576.29</v>
+        <v>602.485</v>
       </c>
       <c r="G24">
         <v>345.7</v>
@@ -3365,28 +3365,28 @@
         <v>528.38</v>
       </c>
       <c r="M24">
-        <v>28.987387</v>
+        <v>30.3049955</v>
       </c>
       <c r="N24">
-        <v>499.392613</v>
+        <v>498.0750045</v>
       </c>
       <c r="O24">
-        <v>124.84815325</v>
+        <v>124.518751125</v>
       </c>
       <c r="P24">
-        <v>374.54445975</v>
+        <v>373.556253375</v>
       </c>
       <c r="Q24">
-        <v>375.66445975</v>
+        <v>374.676253375</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1360517632219954</v>
+        <v>0.1369820019688723</v>
       </c>
       <c r="T24">
-        <v>1.313273123308934</v>
+        <v>1.326809230537433</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3403,7 +3403,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>18.22792789153434</v>
+        <v>17.43540928755459</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3411,22 +3411,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1141528915160316</v>
+        <v>0.1138859077189069</v>
       </c>
       <c r="C25">
-        <v>2120.00168254945</v>
+        <v>2098.725080887559</v>
       </c>
       <c r="D25">
-        <v>2376.78668254945</v>
+        <v>2381.705080887559</v>
       </c>
       <c r="E25">
-        <v>537.1850000000001</v>
+        <v>563.3800000000001</v>
       </c>
       <c r="F25">
-        <v>602.485</v>
+        <v>628.6800000000001</v>
       </c>
       <c r="G25">
         <v>345.7</v>
@@ -3447,28 +3447,28 @@
         <v>528.38</v>
       </c>
       <c r="M25">
-        <v>30.3049955</v>
+        <v>31.622604</v>
       </c>
       <c r="N25">
-        <v>498.0750045</v>
+        <v>496.757396</v>
       </c>
       <c r="O25">
-        <v>124.518751125</v>
+        <v>124.189349</v>
       </c>
       <c r="P25">
-        <v>373.556253375</v>
+        <v>372.568047</v>
       </c>
       <c r="Q25">
-        <v>374.676253375</v>
+        <v>373.688047</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1369820019688723</v>
+        <v>0.1379367206827722</v>
       </c>
       <c r="T25">
-        <v>1.326809230537433</v>
+        <v>1.34070155111405</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3485,7 +3485,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>17.43540928755459</v>
+        <v>16.70893390057314</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3493,22 +3493,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1138859077189069</v>
+        <v>0.1136189239217821</v>
       </c>
       <c r="C26">
-        <v>2098.72508088756</v>
+        <v>2077.4688771899</v>
       </c>
       <c r="D26">
-        <v>2381.70508088756</v>
+        <v>2386.643877189901</v>
       </c>
       <c r="E26">
-        <v>563.38</v>
+        <v>589.575</v>
       </c>
       <c r="F26">
-        <v>628.6799999999999</v>
+        <v>654.875</v>
       </c>
       <c r="G26">
         <v>345.7</v>
@@ -3529,28 +3529,28 @@
         <v>528.38</v>
       </c>
       <c r="M26">
-        <v>31.622604</v>
+        <v>32.9402125</v>
       </c>
       <c r="N26">
-        <v>496.757396</v>
+        <v>495.4397875</v>
       </c>
       <c r="O26">
-        <v>124.189349</v>
+        <v>123.859946875</v>
       </c>
       <c r="P26">
-        <v>372.568047</v>
+        <v>371.579840625</v>
       </c>
       <c r="Q26">
-        <v>373.688047</v>
+        <v>372.699840625</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1379367206827722</v>
+        <v>0.1389168985623762</v>
       </c>
       <c r="T26">
-        <v>1.34070155111405</v>
+        <v>1.35496433357271</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3567,7 +3567,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>16.70893390057315</v>
+        <v>16.04057654455022</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3575,22 +3575,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1136189239217821</v>
+        <v>0.1133519401246574</v>
       </c>
       <c r="C27">
-        <v>2077.4688771899</v>
+        <v>2056.23319861419</v>
       </c>
       <c r="D27">
-        <v>2386.643877189901</v>
+        <v>2391.60319861419</v>
       </c>
       <c r="E27">
-        <v>589.575</v>
+        <v>615.7700000000001</v>
       </c>
       <c r="F27">
-        <v>654.875</v>
+        <v>681.0700000000001</v>
       </c>
       <c r="G27">
         <v>345.7</v>
@@ -3611,28 +3611,28 @@
         <v>528.38</v>
       </c>
       <c r="M27">
-        <v>32.9402125</v>
+        <v>34.257821</v>
       </c>
       <c r="N27">
-        <v>495.4397875</v>
+        <v>494.122179</v>
       </c>
       <c r="O27">
-        <v>123.859946875</v>
+        <v>123.53054475</v>
       </c>
       <c r="P27">
-        <v>371.579840625</v>
+        <v>370.59163425</v>
       </c>
       <c r="Q27">
-        <v>372.699840625</v>
+        <v>371.71163425</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1389168985623762</v>
+        <v>0.1399235677360235</v>
       </c>
       <c r="T27">
-        <v>1.35496433357271</v>
+        <v>1.369612596638361</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3649,7 +3649,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>16.04057654455022</v>
+        <v>15.42363129283675</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3657,22 +3657,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1133519401246574</v>
+        <v>0.1130849563275326</v>
       </c>
       <c r="C28">
-        <v>2056.23319861419</v>
+        <v>2035.018173377251</v>
       </c>
       <c r="D28">
-        <v>2391.60319861419</v>
+        <v>2396.583173377251</v>
       </c>
       <c r="E28">
-        <v>615.7700000000001</v>
+        <v>641.9650000000001</v>
       </c>
       <c r="F28">
-        <v>681.0700000000001</v>
+        <v>707.2650000000001</v>
       </c>
       <c r="G28">
         <v>345.7</v>
@@ -3693,28 +3693,28 @@
         <v>528.38</v>
       </c>
       <c r="M28">
-        <v>34.257821</v>
+        <v>35.57542950000001</v>
       </c>
       <c r="N28">
-        <v>494.122179</v>
+        <v>492.8045705</v>
       </c>
       <c r="O28">
-        <v>123.53054475</v>
+        <v>123.201142625</v>
       </c>
       <c r="P28">
-        <v>370.59163425</v>
+        <v>369.603427875</v>
       </c>
       <c r="Q28">
-        <v>371.71163425</v>
+        <v>370.723427875</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1399235677360235</v>
+        <v>0.140957816887031</v>
       </c>
       <c r="T28">
-        <v>1.369612596638361</v>
+        <v>1.384662181979783</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>15.42363129283675</v>
+        <v>14.85238568939835</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3739,22 +3739,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1130849563275326</v>
+        <v>0.1128179725304079</v>
       </c>
       <c r="C29">
-        <v>2035.018173377251</v>
+        <v>2013.823930766068</v>
       </c>
       <c r="D29">
-        <v>2396.583173377251</v>
+        <v>2401.583930766069</v>
       </c>
       <c r="E29">
-        <v>641.9650000000001</v>
+        <v>668.1600000000001</v>
       </c>
       <c r="F29">
-        <v>707.2650000000001</v>
+        <v>733.46</v>
       </c>
       <c r="G29">
         <v>345.7</v>
@@ -3775,28 +3775,28 @@
         <v>528.38</v>
       </c>
       <c r="M29">
-        <v>35.57542950000001</v>
+        <v>36.893038</v>
       </c>
       <c r="N29">
-        <v>492.8045705</v>
+        <v>491.486962</v>
       </c>
       <c r="O29">
-        <v>123.201142625</v>
+        <v>122.8717405</v>
       </c>
       <c r="P29">
-        <v>369.603427875</v>
+        <v>368.6152215</v>
       </c>
       <c r="Q29">
-        <v>370.723427875</v>
+        <v>369.7352215</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.140957816887031</v>
+        <v>0.142020795181122</v>
       </c>
       <c r="T29">
-        <v>1.384662181979783</v>
+        <v>1.400129811358467</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3813,7 +3813,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>14.85238568939835</v>
+        <v>14.32194334334841</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3821,22 +3821,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1128179725304079</v>
+        <v>0.1125509887332831</v>
       </c>
       <c r="C30">
-        <v>2013.823930766068</v>
+        <v>1992.650601148972</v>
       </c>
       <c r="D30">
-        <v>2401.583930766069</v>
+        <v>2406.605601148972</v>
       </c>
       <c r="E30">
-        <v>668.1600000000001</v>
+        <v>694.3550000000001</v>
       </c>
       <c r="F30">
-        <v>733.46</v>
+        <v>759.6550000000001</v>
       </c>
       <c r="G30">
         <v>345.7</v>
@@ -3857,28 +3857,28 @@
         <v>528.38</v>
       </c>
       <c r="M30">
-        <v>36.893038</v>
+        <v>38.2106465</v>
       </c>
       <c r="N30">
-        <v>491.486962</v>
+        <v>490.1693535</v>
       </c>
       <c r="O30">
-        <v>122.8717405</v>
+        <v>122.542338375</v>
       </c>
       <c r="P30">
-        <v>368.6152215</v>
+        <v>367.627015125</v>
       </c>
       <c r="Q30">
-        <v>369.7352215</v>
+        <v>368.747015125</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.142020795181122</v>
+        <v>0.1431137165257509</v>
       </c>
       <c r="T30">
-        <v>1.400129811358467</v>
+        <v>1.416033148606973</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>14.32194334334841</v>
+        <v>13.82808322806054</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3903,22 +3903,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1125509887332831</v>
+        <v>0.1122840049361583</v>
       </c>
       <c r="C31">
-        <v>1992.650601148972</v>
+        <v>1971.498315986971</v>
       </c>
       <c r="D31">
-        <v>2406.605601148972</v>
+        <v>2411.648315986971</v>
       </c>
       <c r="E31">
-        <v>694.355</v>
+        <v>720.5500000000001</v>
       </c>
       <c r="F31">
-        <v>759.655</v>
+        <v>785.85</v>
       </c>
       <c r="G31">
         <v>345.7</v>
@@ -3939,28 +3939,28 @@
         <v>528.38</v>
       </c>
       <c r="M31">
-        <v>38.2106465</v>
+        <v>39.528255</v>
       </c>
       <c r="N31">
-        <v>490.1693535</v>
+        <v>488.851745</v>
       </c>
       <c r="O31">
-        <v>122.542338375</v>
+        <v>122.21293625</v>
       </c>
       <c r="P31">
-        <v>367.627015125</v>
+        <v>366.63880875</v>
       </c>
       <c r="Q31">
-        <v>368.747015125</v>
+        <v>367.75880875</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1431137165257509</v>
+        <v>0.1442378641945119</v>
       </c>
       <c r="T31">
-        <v>1.416033148606973</v>
+        <v>1.432390866919722</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3977,7 +3977,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>13.82808322806054</v>
+        <v>13.36714712045852</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3985,22 +3985,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1122840049361583</v>
+        <v>0.1120170211390336</v>
       </c>
       <c r="C32">
-        <v>1971.498315986971</v>
+        <v>1950.367207845218</v>
       </c>
       <c r="D32">
-        <v>2411.648315986971</v>
+        <v>2416.712207845218</v>
       </c>
       <c r="E32">
-        <v>720.5500000000001</v>
+        <v>746.745</v>
       </c>
       <c r="F32">
-        <v>785.85</v>
+        <v>812.045</v>
       </c>
       <c r="G32">
         <v>345.7</v>
@@ -4021,28 +4021,28 @@
         <v>528.38</v>
       </c>
       <c r="M32">
-        <v>39.528255</v>
+        <v>40.84586349999999</v>
       </c>
       <c r="N32">
-        <v>488.851745</v>
+        <v>487.5341365</v>
       </c>
       <c r="O32">
-        <v>122.21293625</v>
+        <v>121.883534125</v>
       </c>
       <c r="P32">
-        <v>366.63880875</v>
+        <v>365.650602375</v>
       </c>
       <c r="Q32">
-        <v>367.75880875</v>
+        <v>366.770602375</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1442378641945119</v>
+        <v>0.1453945958536719</v>
       </c>
       <c r="T32">
-        <v>1.432390866919722</v>
+        <v>1.449222721995159</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -4059,7 +4059,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>13.36714712045852</v>
+        <v>12.93594882625018</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4067,22 +4067,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1120170211390336</v>
+        <v>0.1121100373419089</v>
       </c>
       <c r="C33">
-        <v>1950.367207845218</v>
+        <v>1922.405553884118</v>
       </c>
       <c r="D33">
-        <v>2416.712207845218</v>
+        <v>2414.945553884118</v>
       </c>
       <c r="E33">
-        <v>746.745</v>
+        <v>772.9400000000001</v>
       </c>
       <c r="F33">
-        <v>812.045</v>
+        <v>838.24</v>
       </c>
       <c r="G33">
         <v>345.7</v>
@@ -4103,45 +4103,45 @@
         <v>528.38</v>
       </c>
       <c r="M33">
-        <v>40.84586349999999</v>
+        <v>43.420832</v>
       </c>
       <c r="N33">
-        <v>487.5341365</v>
+        <v>484.959168</v>
       </c>
       <c r="O33">
-        <v>121.883534125</v>
+        <v>121.239792</v>
       </c>
       <c r="P33">
-        <v>365.650602375</v>
+        <v>363.719376</v>
       </c>
       <c r="Q33">
-        <v>366.770602375</v>
+        <v>364.839376</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1453945958536719</v>
+        <v>0.1465853490322189</v>
       </c>
       <c r="T33">
-        <v>1.449222721995159</v>
+        <v>1.466549631631639</v>
       </c>
       <c r="U33">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V33">
         <v>0.25</v>
       </c>
       <c r="W33">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y33">
-        <v>12.93594882625018</v>
+        <v>12.1688133474734</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4149,22 +4149,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1121100373419089</v>
+        <v>0.1118543035447841</v>
       </c>
       <c r="C34">
-        <v>1922.405553884118</v>
+        <v>1901.073922072024</v>
       </c>
       <c r="D34">
-        <v>2414.945553884118</v>
+        <v>2419.808922072024</v>
       </c>
       <c r="E34">
-        <v>772.9400000000001</v>
+        <v>799.1350000000001</v>
       </c>
       <c r="F34">
-        <v>838.24</v>
+        <v>864.4350000000001</v>
       </c>
       <c r="G34">
         <v>345.7</v>
@@ -4185,28 +4185,28 @@
         <v>528.38</v>
       </c>
       <c r="M34">
-        <v>43.420832</v>
+        <v>44.777733</v>
       </c>
       <c r="N34">
-        <v>484.959168</v>
+        <v>483.602267</v>
       </c>
       <c r="O34">
-        <v>121.239792</v>
+        <v>120.90056675</v>
       </c>
       <c r="P34">
-        <v>363.719376</v>
+        <v>362.70170025</v>
       </c>
       <c r="Q34">
-        <v>364.839376</v>
+        <v>363.82170025</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1465853490322189</v>
+        <v>0.1478116470817673</v>
       </c>
       <c r="T34">
-        <v>1.466549631631639</v>
+        <v>1.484393762451298</v>
       </c>
       <c r="U34">
         <v>0.0518</v>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>12.1688133474734</v>
+        <v>11.80006142785299</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4231,22 +4231,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1118543035447841</v>
+        <v>0.1115985697476593</v>
       </c>
       <c r="C35">
-        <v>1901.073922072024</v>
+        <v>1879.761918096914</v>
       </c>
       <c r="D35">
-        <v>2419.808922072024</v>
+        <v>2424.691918096914</v>
       </c>
       <c r="E35">
-        <v>799.1350000000001</v>
+        <v>825.3300000000002</v>
       </c>
       <c r="F35">
-        <v>864.4350000000001</v>
+        <v>890.6300000000001</v>
       </c>
       <c r="G35">
         <v>345.7</v>
@@ -4267,28 +4267,28 @@
         <v>528.38</v>
       </c>
       <c r="M35">
-        <v>44.777733</v>
+        <v>46.13463400000001</v>
       </c>
       <c r="N35">
-        <v>483.602267</v>
+        <v>482.245366</v>
       </c>
       <c r="O35">
-        <v>120.90056675</v>
+        <v>120.5613415</v>
       </c>
       <c r="P35">
-        <v>362.70170025</v>
+        <v>361.6840245</v>
       </c>
       <c r="Q35">
-        <v>363.82170025</v>
+        <v>362.8040245</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1478116470817673</v>
+        <v>0.1490751056782718</v>
       </c>
       <c r="T35">
-        <v>1.484393762451298</v>
+        <v>1.502778624507915</v>
       </c>
       <c r="U35">
         <v>0.0518</v>
@@ -4305,7 +4305,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>11.80006142785299</v>
+        <v>11.45300079762202</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4313,22 +4313,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1115985697476593</v>
+        <v>0.1113428359505346</v>
       </c>
       <c r="C36">
-        <v>1879.761918096914</v>
+        <v>1858.469661021634</v>
       </c>
       <c r="D36">
-        <v>2424.691918096914</v>
+        <v>2429.594661021635</v>
       </c>
       <c r="E36">
-        <v>825.3300000000002</v>
+        <v>851.5250000000001</v>
       </c>
       <c r="F36">
-        <v>890.6300000000001</v>
+        <v>916.825</v>
       </c>
       <c r="G36">
         <v>345.7</v>
@@ -4349,28 +4349,28 @@
         <v>528.38</v>
       </c>
       <c r="M36">
-        <v>46.13463400000001</v>
+        <v>47.491535</v>
       </c>
       <c r="N36">
-        <v>482.245366</v>
+        <v>480.888465</v>
       </c>
       <c r="O36">
-        <v>120.5613415</v>
+        <v>120.22211625</v>
       </c>
       <c r="P36">
-        <v>361.6840245</v>
+        <v>360.66634875</v>
       </c>
       <c r="Q36">
-        <v>362.8040245</v>
+        <v>361.78634875</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1490751056782718</v>
+        <v>0.1503774399238994</v>
       </c>
       <c r="T36">
-        <v>1.502778624507915</v>
+        <v>1.521729174627813</v>
       </c>
       <c r="U36">
         <v>0.0518</v>
@@ -4387,7 +4387,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>11.45300079762202</v>
+        <v>11.12577220340425</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1113428359505346</v>
+        <v>0.1110871021534098</v>
       </c>
       <c r="C37">
-        <v>1858.469661021634</v>
+        <v>1837.197270873964</v>
       </c>
       <c r="D37">
-        <v>2429.594661021635</v>
+        <v>2434.517270873964</v>
       </c>
       <c r="E37">
-        <v>851.5250000000001</v>
+        <v>877.7200000000001</v>
       </c>
       <c r="F37">
-        <v>916.825</v>
+        <v>943.0200000000001</v>
       </c>
       <c r="G37">
         <v>345.7</v>
@@ -4431,28 +4431,28 @@
         <v>528.38</v>
       </c>
       <c r="M37">
-        <v>47.491535</v>
+        <v>48.84843600000001</v>
       </c>
       <c r="N37">
-        <v>480.888465</v>
+        <v>479.531564</v>
       </c>
       <c r="O37">
-        <v>120.22211625</v>
+        <v>119.882891</v>
       </c>
       <c r="P37">
-        <v>360.66634875</v>
+        <v>359.648673</v>
       </c>
       <c r="Q37">
-        <v>361.78634875</v>
+        <v>360.768673</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1503774399238994</v>
+        <v>0.1517204721147029</v>
       </c>
       <c r="T37">
-        <v>1.521729174627813</v>
+        <v>1.541271929438958</v>
       </c>
       <c r="U37">
         <v>0.0518</v>
@@ -4469,7 +4469,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>11.12577220340425</v>
+        <v>10.81672297553191</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4477,22 +4477,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1110871021534098</v>
+        <v>0.1108313683562851</v>
       </c>
       <c r="C38">
-        <v>1837.197270873964</v>
+        <v>1815.944868656411</v>
       </c>
       <c r="D38">
-        <v>2434.517270873964</v>
+        <v>2439.459868656411</v>
       </c>
       <c r="E38">
-        <v>877.72</v>
+        <v>903.9150000000001</v>
       </c>
       <c r="F38">
-        <v>943.02</v>
+        <v>969.215</v>
       </c>
       <c r="G38">
         <v>345.7</v>
@@ -4513,28 +4513,28 @@
         <v>528.38</v>
       </c>
       <c r="M38">
-        <v>48.848436</v>
+        <v>50.205337</v>
       </c>
       <c r="N38">
-        <v>479.531564</v>
+        <v>478.174663</v>
       </c>
       <c r="O38">
-        <v>119.882891</v>
+        <v>119.54366575</v>
       </c>
       <c r="P38">
-        <v>359.648673</v>
+        <v>358.63099725</v>
       </c>
       <c r="Q38">
-        <v>360.768673</v>
+        <v>359.75099725</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1517204721147029</v>
+        <v>0.1531061402480716</v>
       </c>
       <c r="T38">
-        <v>1.541271929438958</v>
+        <v>1.561435089164742</v>
       </c>
       <c r="U38">
         <v>0.0518</v>
@@ -4551,7 +4551,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>10.81672297553191</v>
+        <v>10.52437911132834</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4559,22 +4559,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1108313683562851</v>
+        <v>0.1105756345591603</v>
       </c>
       <c r="C39">
-        <v>1815.944868656411</v>
+        <v>1794.712576356128</v>
       </c>
       <c r="D39">
-        <v>2439.459868656411</v>
+        <v>2444.422576356129</v>
       </c>
       <c r="E39">
-        <v>903.9150000000001</v>
+        <v>930.11</v>
       </c>
       <c r="F39">
-        <v>969.215</v>
+        <v>995.41</v>
       </c>
       <c r="G39">
         <v>345.7</v>
@@ -4595,28 +4595,28 @@
         <v>528.38</v>
       </c>
       <c r="M39">
-        <v>50.205337</v>
+        <v>51.562238</v>
       </c>
       <c r="N39">
-        <v>478.174663</v>
+        <v>476.817762</v>
       </c>
       <c r="O39">
-        <v>119.54366575</v>
+        <v>119.2044405</v>
       </c>
       <c r="P39">
-        <v>358.63099725</v>
+        <v>357.6133215</v>
       </c>
       <c r="Q39">
-        <v>359.75099725</v>
+        <v>358.7333215</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1531061402480716</v>
+        <v>0.1545365073534844</v>
       </c>
       <c r="T39">
-        <v>1.561435089164742</v>
+        <v>1.58224867339781</v>
       </c>
       <c r="U39">
         <v>0.0518</v>
@@ -4633,7 +4633,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>10.52437911132834</v>
+        <v>10.24742176629339</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4641,22 +4641,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1105756345591603</v>
+        <v>0.1103199007620356</v>
       </c>
       <c r="C40">
-        <v>1794.712576356128</v>
+        <v>1773.500516954949</v>
       </c>
       <c r="D40">
-        <v>2444.422576356129</v>
+        <v>2449.405516954949</v>
       </c>
       <c r="E40">
-        <v>930.11</v>
+        <v>956.3050000000001</v>
       </c>
       <c r="F40">
-        <v>995.41</v>
+        <v>1021.605</v>
       </c>
       <c r="G40">
         <v>345.7</v>
@@ -4677,28 +4677,28 @@
         <v>528.38</v>
       </c>
       <c r="M40">
-        <v>51.562238</v>
+        <v>52.919139</v>
       </c>
       <c r="N40">
-        <v>476.817762</v>
+        <v>475.460861</v>
       </c>
       <c r="O40">
-        <v>119.2044405</v>
+        <v>118.86521525</v>
       </c>
       <c r="P40">
-        <v>357.6133215</v>
+        <v>356.59564575</v>
       </c>
       <c r="Q40">
-        <v>358.7333215</v>
+        <v>357.71564575</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1545365073534844</v>
+        <v>0.156013771741042</v>
       </c>
       <c r="T40">
-        <v>1.58224867339781</v>
+        <v>1.603744670228683</v>
       </c>
       <c r="U40">
         <v>0.0518</v>
@@ -4715,7 +4715,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>10.24742176629339</v>
+        <v>9.984667362029453</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4723,22 +4723,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1103199007620356</v>
+        <v>0.1105741669649108</v>
       </c>
       <c r="C41">
-        <v>1773.500516954949</v>
+        <v>1742.351114403139</v>
       </c>
       <c r="D41">
-        <v>2449.405516954949</v>
+        <v>2444.451114403139</v>
       </c>
       <c r="E41">
-        <v>956.3050000000001</v>
+        <v>982.5</v>
       </c>
       <c r="F41">
-        <v>1021.605</v>
+        <v>1047.8</v>
       </c>
       <c r="G41">
         <v>345.7</v>
@@ -4759,45 +4759,45 @@
         <v>528.38</v>
       </c>
       <c r="M41">
-        <v>52.919139</v>
+        <v>56.0573</v>
       </c>
       <c r="N41">
-        <v>475.460861</v>
+        <v>472.3227</v>
       </c>
       <c r="O41">
-        <v>118.86521525</v>
+        <v>118.080675</v>
       </c>
       <c r="P41">
-        <v>356.59564575</v>
+        <v>354.242025</v>
       </c>
       <c r="Q41">
-        <v>357.71564575</v>
+        <v>355.362025</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.156013771741042</v>
+        <v>0.1575402782748514</v>
       </c>
       <c r="T41">
-        <v>1.603744670228683</v>
+        <v>1.625957200287252</v>
       </c>
       <c r="U41">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V41">
         <v>0.25</v>
       </c>
       <c r="W41">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y41">
-        <v>9.984667362029453</v>
+        <v>9.425712619052291</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4805,22 +4805,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1105741669649108</v>
+        <v>0.1103311831677861</v>
       </c>
       <c r="C42">
-        <v>1742.351114403139</v>
+        <v>1720.89025238438</v>
       </c>
       <c r="D42">
-        <v>2444.451114403139</v>
+        <v>2449.18525238438</v>
       </c>
       <c r="E42">
-        <v>982.5</v>
+        <v>1008.695</v>
       </c>
       <c r="F42">
-        <v>1047.8</v>
+        <v>1073.995</v>
       </c>
       <c r="G42">
         <v>345.7</v>
@@ -4841,28 +4841,28 @@
         <v>528.38</v>
       </c>
       <c r="M42">
-        <v>56.0573</v>
+        <v>57.4587325</v>
       </c>
       <c r="N42">
-        <v>472.3227</v>
+        <v>470.9212675</v>
       </c>
       <c r="O42">
-        <v>118.080675</v>
+        <v>117.730316875</v>
       </c>
       <c r="P42">
-        <v>354.242025</v>
+        <v>353.190950625</v>
       </c>
       <c r="Q42">
-        <v>355.362025</v>
+        <v>354.310950625</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1575402782748514</v>
+        <v>0.1591185307928578</v>
       </c>
       <c r="T42">
-        <v>1.625957200287252</v>
+        <v>1.648922697466451</v>
       </c>
       <c r="U42">
         <v>0.0535</v>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>9.425712619052291</v>
+        <v>9.195817189319309</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4887,22 +4887,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1103311831677861</v>
+        <v>0.1100881993706613</v>
       </c>
       <c r="C43">
-        <v>1720.89025238438</v>
+        <v>1699.447763039699</v>
       </c>
       <c r="D43">
-        <v>2449.18525238438</v>
+        <v>2453.937763039699</v>
       </c>
       <c r="E43">
-        <v>1008.695</v>
+        <v>1034.89</v>
       </c>
       <c r="F43">
-        <v>1073.995</v>
+        <v>1100.19</v>
       </c>
       <c r="G43">
         <v>345.7</v>
@@ -4923,28 +4923,28 @@
         <v>528.38</v>
       </c>
       <c r="M43">
-        <v>57.4587325</v>
+        <v>58.860165</v>
       </c>
       <c r="N43">
-        <v>470.9212675</v>
+        <v>469.519835</v>
       </c>
       <c r="O43">
-        <v>117.730316875</v>
+        <v>117.37995875</v>
       </c>
       <c r="P43">
-        <v>353.190950625</v>
+        <v>352.13987625</v>
       </c>
       <c r="Q43">
-        <v>354.310950625</v>
+        <v>353.25987625</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1591185307928578</v>
+        <v>0.1607512058114851</v>
       </c>
       <c r="T43">
-        <v>1.648922697466451</v>
+        <v>1.672680108341484</v>
       </c>
       <c r="U43">
         <v>0.0535</v>
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>9.195817189319309</v>
+        <v>8.976869161002181</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4969,22 +4969,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1100881993706614</v>
+        <v>0.1098452155735366</v>
       </c>
       <c r="C44">
-        <v>1699.447763039699</v>
+        <v>1678.023753530559</v>
       </c>
       <c r="D44">
-        <v>2453.937763039699</v>
+        <v>2458.708753530559</v>
       </c>
       <c r="E44">
-        <v>1034.89</v>
+        <v>1061.085</v>
       </c>
       <c r="F44">
-        <v>1100.19</v>
+        <v>1126.385</v>
       </c>
       <c r="G44">
         <v>345.7</v>
@@ -5005,28 +5005,28 @@
         <v>528.38</v>
       </c>
       <c r="M44">
-        <v>58.860165</v>
+        <v>60.2615975</v>
       </c>
       <c r="N44">
-        <v>469.519835</v>
+        <v>468.1184025</v>
       </c>
       <c r="O44">
-        <v>117.37995875</v>
+        <v>117.029600625</v>
       </c>
       <c r="P44">
-        <v>352.13987625</v>
+        <v>351.088801875</v>
       </c>
       <c r="Q44">
-        <v>353.25987625</v>
+        <v>352.208801875</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1607512058114851</v>
+        <v>0.1624411676728712</v>
       </c>
       <c r="T44">
-        <v>1.672680108341484</v>
+        <v>1.697271112580553</v>
       </c>
       <c r="U44">
         <v>0.0535</v>
@@ -5043,7 +5043,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>8.976869161002181</v>
+        <v>8.768104761909107</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5051,22 +5051,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1098452155735366</v>
+        <v>0.1096022317764118</v>
       </c>
       <c r="C45">
-        <v>1678.023753530559</v>
+        <v>1656.618331853427</v>
       </c>
       <c r="D45">
-        <v>2458.708753530559</v>
+        <v>2463.498331853427</v>
       </c>
       <c r="E45">
-        <v>1061.085</v>
+        <v>1087.28</v>
       </c>
       <c r="F45">
-        <v>1126.385</v>
+        <v>1152.58</v>
       </c>
       <c r="G45">
         <v>345.7</v>
@@ -5087,28 +5087,28 @@
         <v>528.38</v>
       </c>
       <c r="M45">
-        <v>60.2615975</v>
+        <v>61.66302999999999</v>
       </c>
       <c r="N45">
-        <v>468.1184025</v>
+        <v>466.71697</v>
       </c>
       <c r="O45">
-        <v>117.029600625</v>
+        <v>116.6792425</v>
       </c>
       <c r="P45">
-        <v>351.088801875</v>
+        <v>350.0377275</v>
       </c>
       <c r="Q45">
-        <v>352.208801875</v>
+        <v>351.1577275</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1624411676728712</v>
+        <v>0.1641914853150211</v>
       </c>
       <c r="T45">
-        <v>1.697271112580553</v>
+        <v>1.722740366971017</v>
       </c>
       <c r="U45">
         <v>0.0535</v>
@@ -5125,7 +5125,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>8.768104761909107</v>
+        <v>8.568829653683903</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5133,22 +5133,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1096022317764118</v>
+        <v>0.1093592479792871</v>
       </c>
       <c r="C46">
-        <v>1656.618331853427</v>
+        <v>1635.231606847924</v>
       </c>
       <c r="D46">
-        <v>2463.498331853427</v>
+        <v>2468.306606847924</v>
       </c>
       <c r="E46">
-        <v>1087.28</v>
+        <v>1113.475</v>
       </c>
       <c r="F46">
-        <v>1152.58</v>
+        <v>1178.775</v>
       </c>
       <c r="G46">
         <v>345.7</v>
@@ -5169,28 +5169,28 @@
         <v>528.38</v>
       </c>
       <c r="M46">
-        <v>61.66302999999999</v>
+        <v>63.0644625</v>
       </c>
       <c r="N46">
-        <v>466.71697</v>
+        <v>465.3155375</v>
       </c>
       <c r="O46">
-        <v>116.6792425</v>
+        <v>116.328884375</v>
       </c>
       <c r="P46">
-        <v>350.0377275</v>
+        <v>348.986653125</v>
       </c>
       <c r="Q46">
-        <v>351.1577275</v>
+        <v>350.106653125</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1641914853150211</v>
+        <v>0.166005450871431</v>
       </c>
       <c r="T46">
-        <v>1.722740366971017</v>
+        <v>1.749135776066589</v>
       </c>
       <c r="U46">
         <v>0.0535</v>
@@ -5207,7 +5207,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>8.568829653683903</v>
+        <v>8.378411216935369</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5215,22 +5215,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1093592479792871</v>
+        <v>0.1091162641821623</v>
       </c>
       <c r="C47">
-        <v>1635.231606847924</v>
+        <v>1613.863688205067</v>
       </c>
       <c r="D47">
-        <v>2468.306606847924</v>
+        <v>2473.133688205067</v>
       </c>
       <c r="E47">
-        <v>1113.475</v>
+        <v>1139.67</v>
       </c>
       <c r="F47">
-        <v>1178.775</v>
+        <v>1204.97</v>
       </c>
       <c r="G47">
         <v>345.7</v>
@@ -5251,28 +5251,28 @@
         <v>528.38</v>
       </c>
       <c r="M47">
-        <v>63.0644625</v>
+        <v>64.465895</v>
       </c>
       <c r="N47">
-        <v>465.3155375</v>
+        <v>463.914105</v>
       </c>
       <c r="O47">
-        <v>116.328884375</v>
+        <v>115.97852625</v>
       </c>
       <c r="P47">
-        <v>348.986653125</v>
+        <v>347.93557875</v>
       </c>
       <c r="Q47">
-        <v>350.106653125</v>
+        <v>349.05557875</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.166005450871431</v>
+        <v>0.1678866003373377</v>
       </c>
       <c r="T47">
-        <v>1.749135776066589</v>
+        <v>1.776508792906442</v>
       </c>
       <c r="U47">
         <v>0.0535</v>
@@ -5289,7 +5289,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>8.378411216935369</v>
+        <v>8.196271842654166</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5297,22 +5297,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1091162641821623</v>
+        <v>0.1088732803850376</v>
       </c>
       <c r="C48">
-        <v>1613.863688205067</v>
+        <v>1592.514686475615</v>
       </c>
       <c r="D48">
-        <v>2473.133688205067</v>
+        <v>2477.979686475615</v>
       </c>
       <c r="E48">
-        <v>1139.67</v>
+        <v>1165.865</v>
       </c>
       <c r="F48">
-        <v>1204.97</v>
+        <v>1231.165</v>
       </c>
       <c r="G48">
         <v>345.7</v>
@@ -5333,28 +5333,28 @@
         <v>528.38</v>
       </c>
       <c r="M48">
-        <v>64.465895</v>
+        <v>65.8673275</v>
       </c>
       <c r="N48">
-        <v>463.914105</v>
+        <v>462.5126725</v>
       </c>
       <c r="O48">
-        <v>115.97852625</v>
+        <v>115.628168125</v>
       </c>
       <c r="P48">
-        <v>347.93557875</v>
+        <v>346.884504375</v>
       </c>
       <c r="Q48">
-        <v>349.05557875</v>
+        <v>348.004504375</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1678866003373377</v>
+        <v>0.1698387365755426</v>
       </c>
       <c r="T48">
-        <v>1.776508792906442</v>
+        <v>1.804914753777987</v>
       </c>
       <c r="U48">
         <v>0.0535</v>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>8.196271842654166</v>
+        <v>8.021883080044503</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5379,22 +5379,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1088732803850376</v>
+        <v>0.1086302965879128</v>
       </c>
       <c r="C49">
-        <v>1592.514686475615</v>
+        <v>1571.184713078503</v>
       </c>
       <c r="D49">
-        <v>2477.979686475615</v>
+        <v>2482.844713078503</v>
       </c>
       <c r="E49">
-        <v>1165.865</v>
+        <v>1192.06</v>
       </c>
       <c r="F49">
-        <v>1231.165</v>
+        <v>1257.36</v>
       </c>
       <c r="G49">
         <v>345.7</v>
@@ -5415,28 +5415,28 @@
         <v>528.38</v>
       </c>
       <c r="M49">
-        <v>65.8673275</v>
+        <v>67.26876</v>
       </c>
       <c r="N49">
-        <v>462.5126725</v>
+        <v>461.11124</v>
       </c>
       <c r="O49">
-        <v>115.628168125</v>
+        <v>115.27781</v>
       </c>
       <c r="P49">
-        <v>346.884504375</v>
+        <v>345.83343</v>
       </c>
       <c r="Q49">
-        <v>348.004504375</v>
+        <v>346.95343</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1698387365755426</v>
+        <v>0.1718659549767554</v>
       </c>
       <c r="T49">
-        <v>1.804914753777987</v>
+        <v>1.834413251606131</v>
       </c>
       <c r="U49">
         <v>0.0535</v>
@@ -5453,7 +5453,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>8.021883080044503</v>
+        <v>7.85476051587691</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1086302965879128</v>
+        <v>0.1083873127907881</v>
       </c>
       <c r="C50">
-        <v>1571.184713078503</v>
+        <v>1549.873880309386</v>
       </c>
       <c r="D50">
-        <v>2482.844713078503</v>
+        <v>2487.728880309387</v>
       </c>
       <c r="E50">
-        <v>1192.06</v>
+        <v>1218.255</v>
       </c>
       <c r="F50">
-        <v>1257.36</v>
+        <v>1283.555</v>
       </c>
       <c r="G50">
         <v>345.7</v>
@@ -5497,28 +5497,28 @@
         <v>528.38</v>
       </c>
       <c r="M50">
-        <v>67.26876</v>
+        <v>68.6701925</v>
       </c>
       <c r="N50">
-        <v>461.11124</v>
+        <v>459.7098075</v>
       </c>
       <c r="O50">
-        <v>115.27781</v>
+        <v>114.927451875</v>
       </c>
       <c r="P50">
-        <v>345.83343</v>
+        <v>344.782355625</v>
       </c>
       <c r="Q50">
-        <v>346.95343</v>
+        <v>345.902355625</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1718659549767554</v>
+        <v>0.1739726721388001</v>
       </c>
       <c r="T50">
-        <v>1.834413251606131</v>
+        <v>1.865068553270671</v>
       </c>
       <c r="U50">
         <v>0.0535</v>
@@ -5535,7 +5535,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>7.85476051587691</v>
+        <v>7.694459280859014</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5543,22 +5543,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1083873127907881</v>
+        <v>0.1084443289936633</v>
       </c>
       <c r="C51">
-        <v>1549.873880309386</v>
+        <v>1522.531084671715</v>
       </c>
       <c r="D51">
-        <v>2487.728880309387</v>
+        <v>2486.581084671715</v>
       </c>
       <c r="E51">
-        <v>1218.255</v>
+        <v>1244.45</v>
       </c>
       <c r="F51">
-        <v>1283.555</v>
+        <v>1309.75</v>
       </c>
       <c r="G51">
         <v>345.7</v>
@@ -5579,45 +5579,45 @@
         <v>528.38</v>
       </c>
       <c r="M51">
-        <v>68.6701925</v>
+        <v>71.11942500000001</v>
       </c>
       <c r="N51">
-        <v>459.7098075</v>
+        <v>457.260575</v>
       </c>
       <c r="O51">
-        <v>114.927451875</v>
+        <v>114.31514375</v>
       </c>
       <c r="P51">
-        <v>344.782355625</v>
+        <v>342.94543125</v>
       </c>
       <c r="Q51">
-        <v>345.902355625</v>
+        <v>344.06543125</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1739726721388001</v>
+        <v>0.1761636579873266</v>
       </c>
       <c r="T51">
-        <v>1.865068553270671</v>
+        <v>1.896950067001794</v>
       </c>
       <c r="U51">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V51">
         <v>0.25</v>
       </c>
       <c r="W51">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y51">
-        <v>7.694459280859014</v>
+        <v>7.429475139879154</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5625,22 +5625,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1084443289936633</v>
+        <v>0.1082073451965386</v>
       </c>
       <c r="C52">
-        <v>1522.531084671715</v>
+        <v>1501.113776778383</v>
       </c>
       <c r="D52">
-        <v>2486.581084671715</v>
+        <v>2491.358776778383</v>
       </c>
       <c r="E52">
-        <v>1244.45</v>
+        <v>1270.645</v>
       </c>
       <c r="F52">
-        <v>1309.75</v>
+        <v>1335.945</v>
       </c>
       <c r="G52">
         <v>345.7</v>
@@ -5661,28 +5661,28 @@
         <v>528.38</v>
       </c>
       <c r="M52">
-        <v>71.11942500000001</v>
+        <v>72.5418135</v>
       </c>
       <c r="N52">
-        <v>457.260575</v>
+        <v>455.8381865</v>
       </c>
       <c r="O52">
-        <v>114.31514375</v>
+        <v>113.959546625</v>
       </c>
       <c r="P52">
-        <v>342.94543125</v>
+        <v>341.878639875</v>
       </c>
       <c r="Q52">
-        <v>344.06543125</v>
+        <v>342.998639875</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1761636579873266</v>
+        <v>0.1784440718296706</v>
       </c>
       <c r="T52">
-        <v>1.896950067001794</v>
+        <v>1.930132867007657</v>
       </c>
       <c r="U52">
         <v>0.0543</v>
@@ -5699,7 +5699,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>7.429475139879154</v>
+        <v>7.283799156744268</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5707,22 +5707,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1082073451965386</v>
+        <v>0.1079703613994138</v>
       </c>
       <c r="C53">
-        <v>1501.113776778383</v>
+        <v>1479.714863848919</v>
       </c>
       <c r="D53">
-        <v>2491.358776778383</v>
+        <v>2496.154863848919</v>
       </c>
       <c r="E53">
-        <v>1270.645</v>
+        <v>1296.84</v>
       </c>
       <c r="F53">
-        <v>1335.945</v>
+        <v>1362.14</v>
       </c>
       <c r="G53">
         <v>345.7</v>
@@ -5743,28 +5743,28 @@
         <v>528.38</v>
       </c>
       <c r="M53">
-        <v>72.5418135</v>
+        <v>73.964202</v>
       </c>
       <c r="N53">
-        <v>455.8381865</v>
+        <v>454.415798</v>
       </c>
       <c r="O53">
-        <v>113.959546625</v>
+        <v>113.6039495</v>
       </c>
       <c r="P53">
-        <v>341.878639875</v>
+        <v>340.8118485</v>
       </c>
       <c r="Q53">
-        <v>342.998639875</v>
+        <v>341.9318485</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1784440718296706</v>
+        <v>0.1808195029154454</v>
       </c>
       <c r="T53">
-        <v>1.930132867007657</v>
+        <v>1.96469828368043</v>
       </c>
       <c r="U53">
         <v>0.0543</v>
@@ -5781,7 +5781,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>7.283799156744268</v>
+        <v>7.143726096037648</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5789,22 +5789,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1079703613994138</v>
+        <v>0.1077333776022891</v>
       </c>
       <c r="C54">
-        <v>1479.714863848919</v>
+        <v>1458.334452324051</v>
       </c>
       <c r="D54">
-        <v>2496.154863848919</v>
+        <v>2500.969452324051</v>
       </c>
       <c r="E54">
-        <v>1296.84</v>
+        <v>1323.035</v>
       </c>
       <c r="F54">
-        <v>1362.14</v>
+        <v>1388.335</v>
       </c>
       <c r="G54">
         <v>345.7</v>
@@ -5825,28 +5825,28 @@
         <v>528.38</v>
       </c>
       <c r="M54">
-        <v>73.964202</v>
+        <v>75.3865905</v>
       </c>
       <c r="N54">
-        <v>454.415798</v>
+        <v>452.9934095</v>
       </c>
       <c r="O54">
-        <v>113.6039495</v>
+        <v>113.248352375</v>
       </c>
       <c r="P54">
-        <v>340.8118485</v>
+        <v>339.745057125</v>
       </c>
       <c r="Q54">
-        <v>341.9318485</v>
+        <v>340.865057125</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1808195029154454</v>
+        <v>0.1832960161750831</v>
       </c>
       <c r="T54">
-        <v>1.96469828368043</v>
+        <v>2.000734569147789</v>
       </c>
       <c r="U54">
         <v>0.0543</v>
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>7.143726096037648</v>
+        <v>7.008938811206749</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5871,22 +5871,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1077333776022891</v>
+        <v>0.1074963938051643</v>
       </c>
       <c r="C55">
-        <v>1458.334452324051</v>
+        <v>1436.972649467308</v>
       </c>
       <c r="D55">
-        <v>2500.969452324051</v>
+        <v>2505.802649467308</v>
       </c>
       <c r="E55">
-        <v>1323.035</v>
+        <v>1349.23</v>
       </c>
       <c r="F55">
-        <v>1388.335</v>
+        <v>1414.53</v>
       </c>
       <c r="G55">
         <v>345.7</v>
@@ -5907,28 +5907,28 @@
         <v>528.38</v>
       </c>
       <c r="M55">
-        <v>75.3865905</v>
+        <v>76.80897900000001</v>
       </c>
       <c r="N55">
-        <v>452.9934095</v>
+        <v>451.571021</v>
       </c>
       <c r="O55">
-        <v>113.248352375</v>
+        <v>112.89275525</v>
       </c>
       <c r="P55">
-        <v>339.745057125</v>
+        <v>338.67826575</v>
       </c>
       <c r="Q55">
-        <v>340.865057125</v>
+        <v>339.79826575</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1832960161750831</v>
+        <v>0.1858802039242702</v>
       </c>
       <c r="T55">
-        <v>2.000734569147789</v>
+        <v>2.038337649635468</v>
       </c>
       <c r="U55">
         <v>0.0543</v>
@@ -5945,7 +5945,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>7.008938811206749</v>
+        <v>6.879143648036253</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5953,22 +5953,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1074963938051643</v>
+        <v>0.1072594100080396</v>
       </c>
       <c r="C56">
-        <v>1436.972649467308</v>
+        <v>1415.629563372982</v>
       </c>
       <c r="D56">
-        <v>2505.802649467308</v>
+        <v>2510.654563372982</v>
       </c>
       <c r="E56">
-        <v>1349.23</v>
+        <v>1375.425</v>
       </c>
       <c r="F56">
-        <v>1414.53</v>
+        <v>1440.725</v>
       </c>
       <c r="G56">
         <v>345.7</v>
@@ -5989,28 +5989,28 @@
         <v>528.38</v>
       </c>
       <c r="M56">
-        <v>76.80897900000001</v>
+        <v>78.2313675</v>
       </c>
       <c r="N56">
-        <v>451.571021</v>
+        <v>450.1486325</v>
       </c>
       <c r="O56">
-        <v>112.89275525</v>
+        <v>112.537158125</v>
       </c>
       <c r="P56">
-        <v>338.67826575</v>
+        <v>337.6114743749999</v>
       </c>
       <c r="Q56">
-        <v>339.79826575</v>
+        <v>338.7314743749999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1858802039242702</v>
+        <v>0.1885792444623101</v>
       </c>
       <c r="T56">
-        <v>2.038337649635468</v>
+        <v>2.077611978144823</v>
       </c>
       <c r="U56">
         <v>0.0543</v>
@@ -6027,7 +6027,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>6.879143648036253</v>
+        <v>6.754068308981048</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6035,22 +6035,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1072594100080396</v>
+        <v>0.1070224262109148</v>
       </c>
       <c r="C57">
-        <v>1415.629563372982</v>
+        <v>1394.305302974193</v>
       </c>
       <c r="D57">
-        <v>2510.654563372982</v>
+        <v>2515.525302974193</v>
       </c>
       <c r="E57">
-        <v>1375.425</v>
+        <v>1401.62</v>
       </c>
       <c r="F57">
-        <v>1440.725</v>
+        <v>1466.92</v>
       </c>
       <c r="G57">
         <v>345.7</v>
@@ -6071,28 +6071,28 @@
         <v>528.38</v>
       </c>
       <c r="M57">
-        <v>78.2313675</v>
+        <v>79.653756</v>
       </c>
       <c r="N57">
-        <v>450.1486325</v>
+        <v>448.726244</v>
       </c>
       <c r="O57">
-        <v>112.537158125</v>
+        <v>112.181561</v>
       </c>
       <c r="P57">
-        <v>337.6114743749999</v>
+        <v>336.544683</v>
       </c>
       <c r="Q57">
-        <v>338.7314743749999</v>
+        <v>337.664683</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1885792444623101</v>
+        <v>0.19140096866117</v>
       </c>
       <c r="T57">
-        <v>2.077611978144823</v>
+        <v>2.118671503404602</v>
       </c>
       <c r="U57">
         <v>0.0543</v>
@@ -6109,7 +6109,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>6.754068308981048</v>
+        <v>6.633459946320674</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6117,22 +6117,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1070224262109148</v>
+        <v>0.1067854424137901</v>
       </c>
       <c r="C58">
-        <v>1394.305302974193</v>
+        <v>1372.99997805103</v>
       </c>
       <c r="D58">
-        <v>2515.525302974193</v>
+        <v>2520.414978051031</v>
       </c>
       <c r="E58">
-        <v>1401.62</v>
+        <v>1427.815</v>
       </c>
       <c r="F58">
-        <v>1466.92</v>
+        <v>1493.115</v>
       </c>
       <c r="G58">
         <v>345.7</v>
@@ -6153,28 +6153,28 @@
         <v>528.38</v>
       </c>
       <c r="M58">
-        <v>79.653756</v>
+        <v>81.07614450000001</v>
       </c>
       <c r="N58">
-        <v>448.726244</v>
+        <v>447.3038555</v>
       </c>
       <c r="O58">
-        <v>112.181561</v>
+        <v>111.825963875</v>
       </c>
       <c r="P58">
-        <v>336.544683</v>
+        <v>335.477891625</v>
       </c>
       <c r="Q58">
-        <v>337.664683</v>
+        <v>336.597891625</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.19140096866117</v>
+        <v>0.1943539358460234</v>
       </c>
       <c r="T58">
-        <v>2.118671503404602</v>
+        <v>2.161640774025301</v>
       </c>
       <c r="U58">
         <v>0.0543</v>
@@ -6191,7 +6191,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>6.633459946320674</v>
+        <v>6.517083456034345</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6199,22 +6199,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1067854424137901</v>
+        <v>0.1065484586166653</v>
       </c>
       <c r="C59">
-        <v>1372.99997805103</v>
+        <v>1351.713699238814</v>
       </c>
       <c r="D59">
-        <v>2520.414978051031</v>
+        <v>2525.323699238815</v>
       </c>
       <c r="E59">
-        <v>1427.815</v>
+        <v>1454.01</v>
       </c>
       <c r="F59">
-        <v>1493.115</v>
+        <v>1519.31</v>
       </c>
       <c r="G59">
         <v>345.7</v>
@@ -6235,28 +6235,28 @@
         <v>528.38</v>
       </c>
       <c r="M59">
-        <v>81.07614450000001</v>
+        <v>82.49853300000001</v>
       </c>
       <c r="N59">
-        <v>447.3038555</v>
+        <v>445.881467</v>
       </c>
       <c r="O59">
-        <v>111.825963875</v>
+        <v>111.47036675</v>
       </c>
       <c r="P59">
-        <v>335.477891625</v>
+        <v>334.41110025</v>
       </c>
       <c r="Q59">
-        <v>336.597891625</v>
+        <v>335.53110025</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1943539358460234</v>
+        <v>0.1974475205158698</v>
       </c>
       <c r="T59">
-        <v>2.161640774025301</v>
+        <v>2.206656200389843</v>
       </c>
       <c r="U59">
         <v>0.0543</v>
@@ -6273,7 +6273,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>6.517083456034345</v>
+        <v>6.404719948171683</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6281,22 +6281,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1065484586166653</v>
+        <v>0.1063114748195405</v>
       </c>
       <c r="C60">
-        <v>1351.713699238815</v>
+        <v>1330.446578036431</v>
       </c>
       <c r="D60">
-        <v>2525.323699238815</v>
+        <v>2530.251578036432</v>
       </c>
       <c r="E60">
-        <v>1454.01</v>
+        <v>1480.205</v>
       </c>
       <c r="F60">
-        <v>1519.31</v>
+        <v>1545.505</v>
       </c>
       <c r="G60">
         <v>345.7</v>
@@ -6317,28 +6317,28 @@
         <v>528.38</v>
       </c>
       <c r="M60">
-        <v>82.49853299999999</v>
+        <v>83.92092149999999</v>
       </c>
       <c r="N60">
-        <v>445.881467</v>
+        <v>444.4590785</v>
       </c>
       <c r="O60">
-        <v>111.47036675</v>
+        <v>111.114769625</v>
       </c>
       <c r="P60">
-        <v>334.41110025</v>
+        <v>333.344308875</v>
       </c>
       <c r="Q60">
-        <v>335.53110025</v>
+        <v>334.464308875</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1974475205158698</v>
+        <v>0.2006920117549769</v>
       </c>
       <c r="T60">
-        <v>2.206656200389842</v>
+        <v>2.253867501211191</v>
       </c>
       <c r="U60">
         <v>0.0543</v>
@@ -6355,7 +6355,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>6.404719948171684</v>
+        <v>6.296165372778945</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6363,22 +6363,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1063114748195405</v>
+        <v>0.1060744910224158</v>
       </c>
       <c r="C61">
-        <v>1330.446578036431</v>
+        <v>1309.198726814776</v>
       </c>
       <c r="D61">
-        <v>2530.251578036432</v>
+        <v>2535.198726814776</v>
       </c>
       <c r="E61">
-        <v>1480.205</v>
+        <v>1506.4</v>
       </c>
       <c r="F61">
-        <v>1545.505</v>
+        <v>1571.7</v>
       </c>
       <c r="G61">
         <v>345.7</v>
@@ -6399,28 +6399,28 @@
         <v>528.38</v>
       </c>
       <c r="M61">
-        <v>83.92092149999999</v>
+        <v>85.34331</v>
       </c>
       <c r="N61">
-        <v>444.4590785</v>
+        <v>443.03669</v>
       </c>
       <c r="O61">
-        <v>111.114769625</v>
+        <v>110.7591725</v>
       </c>
       <c r="P61">
-        <v>333.344308875</v>
+        <v>332.2775175</v>
       </c>
       <c r="Q61">
-        <v>334.464308875</v>
+        <v>333.3975175</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2006920117549769</v>
+        <v>0.2040987275560395</v>
       </c>
       <c r="T61">
-        <v>2.253867501211191</v>
+        <v>2.303439367073607</v>
       </c>
       <c r="U61">
         <v>0.0543</v>
@@ -6437,7 +6437,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>6.296165372778945</v>
+        <v>6.191229283232628</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6445,22 +6445,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1060744910224158</v>
+        <v>0.106295007225291</v>
       </c>
       <c r="C62">
-        <v>1309.198726814776</v>
+        <v>1278.399722554534</v>
       </c>
       <c r="D62">
-        <v>2535.198726814776</v>
+        <v>2530.594722554534</v>
       </c>
       <c r="E62">
-        <v>1506.4</v>
+        <v>1532.595</v>
       </c>
       <c r="F62">
-        <v>1571.7</v>
+        <v>1597.895</v>
       </c>
       <c r="G62">
         <v>345.7</v>
@@ -6481,45 +6481,45 @@
         <v>528.38</v>
       </c>
       <c r="M62">
-        <v>85.34331</v>
+        <v>88.36359350000001</v>
       </c>
       <c r="N62">
-        <v>443.03669</v>
+        <v>440.0164065</v>
       </c>
       <c r="O62">
-        <v>110.7591725</v>
+        <v>110.004101625</v>
       </c>
       <c r="P62">
-        <v>332.2775175</v>
+        <v>330.012304875</v>
       </c>
       <c r="Q62">
-        <v>333.3975175</v>
+        <v>331.132304875</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2040987275560395</v>
+        <v>0.2076801467315155</v>
       </c>
       <c r="T62">
-        <v>2.303439367073607</v>
+        <v>2.355553379903327</v>
       </c>
       <c r="U62">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V62">
         <v>0.25</v>
       </c>
       <c r="W62">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y62">
-        <v>6.191229283232628</v>
+        <v>5.979611954101889</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.106295007225291</v>
+        <v>0.1060655234281663</v>
       </c>
       <c r="C63">
-        <v>1278.399722554534</v>
+        <v>1256.996309480759</v>
       </c>
       <c r="D63">
-        <v>2530.594722554534</v>
+        <v>2535.386309480759</v>
       </c>
       <c r="E63">
-        <v>1532.595</v>
+        <v>1558.79</v>
       </c>
       <c r="F63">
-        <v>1597.895</v>
+        <v>1624.09</v>
       </c>
       <c r="G63">
         <v>345.7</v>
@@ -6563,28 +6563,28 @@
         <v>528.38</v>
       </c>
       <c r="M63">
-        <v>88.36359350000001</v>
+        <v>89.81217700000001</v>
       </c>
       <c r="N63">
-        <v>440.0164065</v>
+        <v>438.567823</v>
       </c>
       <c r="O63">
-        <v>110.004101625</v>
+        <v>109.64195575</v>
       </c>
       <c r="P63">
-        <v>330.012304875</v>
+        <v>328.92586725</v>
       </c>
       <c r="Q63">
-        <v>331.132304875</v>
+        <v>330.04586725</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2076801467315155</v>
+        <v>0.2114500616530692</v>
       </c>
       <c r="T63">
-        <v>2.355553379903327</v>
+        <v>2.410410235513558</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6601,7 +6601,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>5.979611954101889</v>
+        <v>5.883166600003471</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6609,22 +6609,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1060655234281663</v>
+        <v>0.1058360396310415</v>
       </c>
       <c r="C64">
-        <v>1256.996309480759</v>
+        <v>1235.611076212803</v>
       </c>
       <c r="D64">
-        <v>2535.386309480759</v>
+        <v>2540.196076212804</v>
       </c>
       <c r="E64">
-        <v>1558.79</v>
+        <v>1584.985</v>
       </c>
       <c r="F64">
-        <v>1624.09</v>
+        <v>1650.285</v>
       </c>
       <c r="G64">
         <v>345.7</v>
@@ -6645,28 +6645,28 @@
         <v>528.38</v>
       </c>
       <c r="M64">
-        <v>89.81217700000001</v>
+        <v>91.2607605</v>
       </c>
       <c r="N64">
-        <v>438.567823</v>
+        <v>437.1192395</v>
       </c>
       <c r="O64">
-        <v>109.64195575</v>
+        <v>109.279809875</v>
       </c>
       <c r="P64">
-        <v>328.92586725</v>
+        <v>327.839429625</v>
       </c>
       <c r="Q64">
-        <v>330.04586725</v>
+        <v>328.959429625</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2114500616530692</v>
+        <v>0.2154237557595717</v>
       </c>
       <c r="T64">
-        <v>2.410410235513558</v>
+        <v>2.46823232656218</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6683,7 +6683,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>5.883166600003471</v>
+        <v>5.78978300317802</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6691,22 +6691,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1058360396310415</v>
+        <v>0.1056065558339168</v>
       </c>
       <c r="C65">
-        <v>1235.611076212803</v>
+        <v>1214.244126411581</v>
       </c>
       <c r="D65">
-        <v>2540.196076212804</v>
+        <v>2545.024126411581</v>
       </c>
       <c r="E65">
-        <v>1584.985</v>
+        <v>1611.18</v>
       </c>
       <c r="F65">
-        <v>1650.285</v>
+        <v>1676.48</v>
       </c>
       <c r="G65">
         <v>345.7</v>
@@ -6727,28 +6727,28 @@
         <v>528.38</v>
       </c>
       <c r="M65">
-        <v>91.2607605</v>
+        <v>92.709344</v>
       </c>
       <c r="N65">
-        <v>437.1192395</v>
+        <v>435.670656</v>
       </c>
       <c r="O65">
-        <v>109.279809875</v>
+        <v>108.917664</v>
       </c>
       <c r="P65">
-        <v>327.839429625</v>
+        <v>326.752992</v>
       </c>
       <c r="Q65">
-        <v>328.959429625</v>
+        <v>327.872992</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2154237557595717</v>
+        <v>0.2196182106497689</v>
       </c>
       <c r="T65">
-        <v>2.46823232656218</v>
+        <v>2.529266756002392</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6765,7 +6765,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>5.78978300317802</v>
+        <v>5.699317643753363</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6773,22 +6773,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1056065558339168</v>
+        <v>0.105377072036792</v>
       </c>
       <c r="C66">
-        <v>1214.244126411581</v>
+        <v>1192.8955645276</v>
       </c>
       <c r="D66">
-        <v>2545.024126411581</v>
+        <v>2549.8705645276</v>
       </c>
       <c r="E66">
-        <v>1611.18</v>
+        <v>1637.375</v>
       </c>
       <c r="F66">
-        <v>1676.48</v>
+        <v>1702.675</v>
       </c>
       <c r="G66">
         <v>345.7</v>
@@ -6809,28 +6809,28 @@
         <v>528.38</v>
       </c>
       <c r="M66">
-        <v>92.709344</v>
+        <v>94.1579275</v>
       </c>
       <c r="N66">
-        <v>435.670656</v>
+        <v>434.2220725</v>
       </c>
       <c r="O66">
-        <v>108.917664</v>
+        <v>108.555518125</v>
       </c>
       <c r="P66">
-        <v>326.752992</v>
+        <v>325.666554375</v>
       </c>
       <c r="Q66">
-        <v>327.872992</v>
+        <v>326.786554375</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2196182106497689</v>
+        <v>0.2240523486765487</v>
       </c>
       <c r="T66">
-        <v>2.529266756002392</v>
+        <v>2.593788867124903</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6847,7 +6847,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>5.699317643753363</v>
+        <v>5.611635833849465</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6855,22 +6855,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.105377072036792</v>
+        <v>0.1051475882396673</v>
       </c>
       <c r="C67">
-        <v>1192.8955645276</v>
+        <v>1171.565495808505</v>
       </c>
       <c r="D67">
-        <v>2549.8705645276</v>
+        <v>2554.735495808505</v>
       </c>
       <c r="E67">
-        <v>1637.375</v>
+        <v>1663.57</v>
       </c>
       <c r="F67">
-        <v>1702.675</v>
+        <v>1728.87</v>
       </c>
       <c r="G67">
         <v>345.7</v>
@@ -6891,28 +6891,28 @@
         <v>528.38</v>
       </c>
       <c r="M67">
-        <v>94.1579275</v>
+        <v>95.60651100000001</v>
       </c>
       <c r="N67">
-        <v>434.2220725</v>
+        <v>432.773489</v>
       </c>
       <c r="O67">
-        <v>108.555518125</v>
+        <v>108.19337225</v>
       </c>
       <c r="P67">
-        <v>325.666554375</v>
+        <v>324.58011675</v>
       </c>
       <c r="Q67">
-        <v>326.786554375</v>
+        <v>325.70011675</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2240523486765487</v>
+        <v>0.2287473183519626</v>
       </c>
       <c r="T67">
-        <v>2.593788867124903</v>
+        <v>2.662106396548737</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6929,7 +6929,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>5.611635833849465</v>
+        <v>5.526611048488109</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6937,22 +6937,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1051475882396673</v>
+        <v>0.1049181044425425</v>
       </c>
       <c r="C68">
-        <v>1171.565495808505</v>
+        <v>1150.254026306683</v>
       </c>
       <c r="D68">
-        <v>2554.735495808505</v>
+        <v>2559.619026306683</v>
       </c>
       <c r="E68">
-        <v>1663.57</v>
+        <v>1689.765</v>
       </c>
       <c r="F68">
-        <v>1728.87</v>
+        <v>1755.065</v>
       </c>
       <c r="G68">
         <v>345.7</v>
@@ -6973,28 +6973,28 @@
         <v>528.38</v>
       </c>
       <c r="M68">
-        <v>95.60651100000001</v>
+        <v>97.05509450000001</v>
       </c>
       <c r="N68">
-        <v>432.773489</v>
+        <v>431.3249055</v>
       </c>
       <c r="O68">
-        <v>108.19337225</v>
+        <v>107.831226375</v>
       </c>
       <c r="P68">
-        <v>324.58011675</v>
+        <v>323.493679125</v>
       </c>
       <c r="Q68">
-        <v>325.70011675</v>
+        <v>324.613679125</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2287473183519626</v>
+        <v>0.2337268316440683</v>
       </c>
       <c r="T68">
-        <v>2.662106396548737</v>
+        <v>2.734564382301288</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -7011,7 +7011,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>5.526611048488109</v>
+        <v>5.444124316421123</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7019,22 +7019,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1049181044425425</v>
+        <v>0.1046886206454178</v>
       </c>
       <c r="C69">
-        <v>1150.254026306683</v>
+        <v>1128.96126288698</v>
       </c>
       <c r="D69">
-        <v>2559.619026306683</v>
+        <v>2564.52126288698</v>
       </c>
       <c r="E69">
-        <v>1689.765</v>
+        <v>1715.96</v>
       </c>
       <c r="F69">
-        <v>1755.065</v>
+        <v>1781.26</v>
       </c>
       <c r="G69">
         <v>345.7</v>
@@ -7055,28 +7055,28 @@
         <v>528.38</v>
       </c>
       <c r="M69">
-        <v>97.05509450000001</v>
+        <v>98.50367800000002</v>
       </c>
       <c r="N69">
-        <v>431.3249055</v>
+        <v>429.876322</v>
       </c>
       <c r="O69">
-        <v>107.831226375</v>
+        <v>107.4690805</v>
       </c>
       <c r="P69">
-        <v>323.493679125</v>
+        <v>322.4072414999999</v>
       </c>
       <c r="Q69">
-        <v>324.613679125</v>
+        <v>323.5272414999999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2337268316440683</v>
+        <v>0.2390175645169306</v>
       </c>
       <c r="T69">
-        <v>2.734564382301288</v>
+        <v>2.811550992163374</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -7093,7 +7093,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>5.444124316421123</v>
+        <v>5.364063664709047</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7101,22 +7101,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1046886206454178</v>
+        <v>0.104459136848293</v>
       </c>
       <c r="C70">
-        <v>1128.96126288698</v>
+        <v>1107.68731323449</v>
       </c>
       <c r="D70">
-        <v>2564.52126288698</v>
+        <v>2569.44231323449</v>
       </c>
       <c r="E70">
-        <v>1715.96</v>
+        <v>1742.155</v>
       </c>
       <c r="F70">
-        <v>1781.26</v>
+        <v>1807.455</v>
       </c>
       <c r="G70">
         <v>345.7</v>
@@ -7137,28 +7137,28 @@
         <v>528.38</v>
       </c>
       <c r="M70">
-        <v>98.50367800000002</v>
+        <v>99.95226150000001</v>
       </c>
       <c r="N70">
-        <v>429.876322</v>
+        <v>428.4277385</v>
       </c>
       <c r="O70">
-        <v>107.4690805</v>
+        <v>107.106934625</v>
       </c>
       <c r="P70">
-        <v>322.4072414999999</v>
+        <v>321.320803875</v>
       </c>
       <c r="Q70">
-        <v>323.5272414999999</v>
+        <v>322.440803875</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2390175645169306</v>
+        <v>0.2446496349944937</v>
       </c>
       <c r="T70">
-        <v>2.811550992163374</v>
+        <v>2.893504480081079</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7175,7 +7175,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>5.364063664709047</v>
+        <v>5.286323611597322</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7183,22 +7183,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.104459136848293</v>
+        <v>0.1042296530511683</v>
       </c>
       <c r="C71">
-        <v>1107.68731323449</v>
+        <v>1086.432285862444</v>
       </c>
       <c r="D71">
-        <v>2569.44231323449</v>
+        <v>2574.382285862444</v>
       </c>
       <c r="E71">
-        <v>1742.155</v>
+        <v>1768.35</v>
       </c>
       <c r="F71">
-        <v>1807.455</v>
+        <v>1833.65</v>
       </c>
       <c r="G71">
         <v>345.7</v>
@@ -7219,28 +7219,28 @@
         <v>528.38</v>
       </c>
       <c r="M71">
-        <v>99.95226150000001</v>
+        <v>101.400845</v>
       </c>
       <c r="N71">
-        <v>428.4277385</v>
+        <v>426.979155</v>
       </c>
       <c r="O71">
-        <v>107.106934625</v>
+        <v>106.74478875</v>
       </c>
       <c r="P71">
-        <v>321.320803875</v>
+        <v>320.23436625</v>
       </c>
       <c r="Q71">
-        <v>322.440803875</v>
+        <v>321.35436625</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2446496349944937</v>
+        <v>0.2506571768372276</v>
       </c>
       <c r="T71">
-        <v>2.893504480081079</v>
+        <v>2.980921533859963</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7257,7 +7257,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>5.286323611597322</v>
+        <v>5.210804702860218</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7265,22 +7265,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1042296530511683</v>
+        <v>0.1040001692540435</v>
       </c>
       <c r="C72">
-        <v>1086.432285862444</v>
+        <v>1065.196290120183</v>
       </c>
       <c r="D72">
-        <v>2574.382285862444</v>
+        <v>2579.341290120184</v>
       </c>
       <c r="E72">
-        <v>1768.35</v>
+        <v>1794.545</v>
       </c>
       <c r="F72">
-        <v>1833.65</v>
+        <v>1859.845</v>
       </c>
       <c r="G72">
         <v>345.7</v>
@@ -7301,28 +7301,28 @@
         <v>528.38</v>
       </c>
       <c r="M72">
-        <v>101.400845</v>
+        <v>102.8494285</v>
       </c>
       <c r="N72">
-        <v>426.979155</v>
+        <v>425.5305715</v>
       </c>
       <c r="O72">
-        <v>106.74478875</v>
+        <v>106.382642875</v>
       </c>
       <c r="P72">
-        <v>320.23436625</v>
+        <v>319.147928625</v>
       </c>
       <c r="Q72">
-        <v>321.35436625</v>
+        <v>320.267928625</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2506571768372276</v>
+        <v>0.257079031910495</v>
       </c>
       <c r="T72">
-        <v>2.980921533859963</v>
+        <v>3.074367349968426</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7339,7 +7339,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>5.210804702860218</v>
+        <v>5.137413087326975</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7347,22 +7347,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1040001692540435</v>
+        <v>0.1037706854569188</v>
       </c>
       <c r="C73">
-        <v>1065.196290120184</v>
+        <v>1043.979436201229</v>
       </c>
       <c r="D73">
-        <v>2579.341290120184</v>
+        <v>2584.31943620123</v>
       </c>
       <c r="E73">
-        <v>1794.545</v>
+        <v>1820.74</v>
       </c>
       <c r="F73">
-        <v>1859.845</v>
+        <v>1886.04</v>
       </c>
       <c r="G73">
         <v>345.7</v>
@@ -7383,28 +7383,28 @@
         <v>528.38</v>
       </c>
       <c r="M73">
-        <v>102.8494285</v>
+        <v>104.298012</v>
       </c>
       <c r="N73">
-        <v>425.5305715</v>
+        <v>424.081988</v>
       </c>
       <c r="O73">
-        <v>106.382642875</v>
+        <v>106.020497</v>
       </c>
       <c r="P73">
-        <v>319.147928625</v>
+        <v>318.061491</v>
       </c>
       <c r="Q73">
-        <v>320.267928625</v>
+        <v>319.1814910000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2570790319104949</v>
+        <v>0.263959590917567</v>
       </c>
       <c r="T73">
-        <v>3.074367349968425</v>
+        <v>3.174487867227492</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7421,7 +7421,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>5.137413087326975</v>
+        <v>5.066060127780768</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7429,22 +7429,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1037706854569188</v>
+        <v>0.103541201659794</v>
       </c>
       <c r="C74">
-        <v>1043.979436201229</v>
+        <v>1022.781835151445</v>
       </c>
       <c r="D74">
-        <v>2584.31943620123</v>
+        <v>2589.316835151446</v>
       </c>
       <c r="E74">
-        <v>1820.74</v>
+        <v>1846.935</v>
       </c>
       <c r="F74">
-        <v>1886.04</v>
+        <v>1912.235</v>
       </c>
       <c r="G74">
         <v>345.7</v>
@@ -7465,28 +7465,28 @@
         <v>528.38</v>
       </c>
       <c r="M74">
-        <v>104.298012</v>
+        <v>105.7465955</v>
       </c>
       <c r="N74">
-        <v>424.081988</v>
+        <v>422.6334045</v>
       </c>
       <c r="O74">
-        <v>106.020497</v>
+        <v>105.658351125</v>
       </c>
       <c r="P74">
-        <v>318.061491</v>
+        <v>316.975053375</v>
       </c>
       <c r="Q74">
-        <v>319.1814910000001</v>
+        <v>318.095053375</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.263959590917567</v>
+        <v>0.2713498209622001</v>
       </c>
       <c r="T74">
-        <v>3.174487867227492</v>
+        <v>3.282024719098342</v>
       </c>
       <c r="U74">
         <v>0.0553</v>
@@ -7503,7 +7503,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>5.066060127780768</v>
+        <v>4.996662043838565</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7511,22 +7511,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.103541201659794</v>
+        <v>0.1033117178626693</v>
       </c>
       <c r="C75">
-        <v>1022.781835151445</v>
+        <v>1001.603598877294</v>
       </c>
       <c r="D75">
-        <v>2589.316835151446</v>
+        <v>2594.333598877294</v>
       </c>
       <c r="E75">
-        <v>1846.935</v>
+        <v>1873.13</v>
       </c>
       <c r="F75">
-        <v>1912.235</v>
+        <v>1938.43</v>
       </c>
       <c r="G75">
         <v>345.7</v>
@@ -7547,28 +7547,28 @@
         <v>528.38</v>
       </c>
       <c r="M75">
-        <v>105.7465955</v>
+        <v>107.195179</v>
       </c>
       <c r="N75">
-        <v>422.6334045</v>
+        <v>421.184821</v>
       </c>
       <c r="O75">
-        <v>105.658351125</v>
+        <v>105.29620525</v>
       </c>
       <c r="P75">
-        <v>316.975053375</v>
+        <v>315.88861575</v>
       </c>
       <c r="Q75">
-        <v>318.095053375</v>
+        <v>317.00861575</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2713498209622001</v>
+        <v>0.2793085302410356</v>
       </c>
       <c r="T75">
-        <v>3.282024719098342</v>
+        <v>3.397833636497719</v>
       </c>
       <c r="U75">
         <v>0.0553</v>
@@ -7585,7 +7585,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>4.996662043838565</v>
+        <v>4.929139583786692</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7593,22 +7593,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1033117178626693</v>
+        <v>0.1030822340655445</v>
       </c>
       <c r="C76">
-        <v>1001.603598877294</v>
+        <v>980.4448401541895</v>
       </c>
       <c r="D76">
-        <v>2594.333598877294</v>
+        <v>2599.36984015419</v>
       </c>
       <c r="E76">
-        <v>1873.13</v>
+        <v>1899.325</v>
       </c>
       <c r="F76">
-        <v>1938.43</v>
+        <v>1964.625</v>
       </c>
       <c r="G76">
         <v>345.7</v>
@@ -7629,28 +7629,28 @@
         <v>528.38</v>
       </c>
       <c r="M76">
-        <v>107.195179</v>
+        <v>108.6437625</v>
       </c>
       <c r="N76">
-        <v>421.184821</v>
+        <v>419.7362375</v>
       </c>
       <c r="O76">
-        <v>105.29620525</v>
+        <v>104.934059375</v>
       </c>
       <c r="P76">
-        <v>315.88861575</v>
+        <v>314.802178125</v>
       </c>
       <c r="Q76">
-        <v>317.00861575</v>
+        <v>315.922178125</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2793085302410356</v>
+        <v>0.287903936262178</v>
       </c>
       <c r="T76">
-        <v>3.397833636497719</v>
+        <v>3.522907267289046</v>
       </c>
       <c r="U76">
         <v>0.0553</v>
@@ -7667,7 +7667,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>4.929139583786692</v>
+        <v>4.863417722669537</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7675,22 +7675,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1030822340655445</v>
+        <v>0.1028527502684198</v>
       </c>
       <c r="C77">
-        <v>980.4448401541895</v>
+        <v>959.3056726349494</v>
       </c>
       <c r="D77">
-        <v>2599.36984015419</v>
+        <v>2604.425672634949</v>
       </c>
       <c r="E77">
-        <v>1899.325</v>
+        <v>1925.52</v>
       </c>
       <c r="F77">
-        <v>1964.625</v>
+        <v>1990.82</v>
       </c>
       <c r="G77">
         <v>345.7</v>
@@ -7711,28 +7711,28 @@
         <v>528.38</v>
       </c>
       <c r="M77">
-        <v>108.6437625</v>
+        <v>110.092346</v>
       </c>
       <c r="N77">
-        <v>419.7362375</v>
+        <v>418.287654</v>
       </c>
       <c r="O77">
-        <v>104.934059375</v>
+        <v>104.5719135</v>
       </c>
       <c r="P77">
-        <v>314.802178125</v>
+        <v>313.7157405</v>
       </c>
       <c r="Q77">
-        <v>315.922178125</v>
+        <v>314.8357405</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.287903936262178</v>
+        <v>0.2972156261184157</v>
       </c>
       <c r="T77">
-        <v>3.522907267289046</v>
+        <v>3.658403700646318</v>
       </c>
       <c r="U77">
         <v>0.0553</v>
@@ -7749,7 +7749,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>4.863417722669537</v>
+        <v>4.799425384213357</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7757,22 +7757,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1028527502684198</v>
+        <v>0.102623266471295</v>
       </c>
       <c r="C78">
-        <v>959.3056726349494</v>
+        <v>938.186210858343</v>
       </c>
       <c r="D78">
-        <v>2604.425672634949</v>
+        <v>2609.501210858343</v>
       </c>
       <c r="E78">
-        <v>1925.52</v>
+        <v>1951.715</v>
       </c>
       <c r="F78">
-        <v>1990.82</v>
+        <v>2017.015</v>
       </c>
       <c r="G78">
         <v>345.7</v>
@@ -7793,28 +7793,28 @@
         <v>528.38</v>
       </c>
       <c r="M78">
-        <v>110.092346</v>
+        <v>111.5409295</v>
       </c>
       <c r="N78">
-        <v>418.287654</v>
+        <v>416.8390705</v>
       </c>
       <c r="O78">
-        <v>104.5719135</v>
+        <v>104.209767625</v>
       </c>
       <c r="P78">
-        <v>313.7157405</v>
+        <v>312.629302875</v>
       </c>
       <c r="Q78">
-        <v>314.8357405</v>
+        <v>313.749302875</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2972156261184157</v>
+        <v>0.3073370281360653</v>
       </c>
       <c r="T78">
-        <v>3.658403700646318</v>
+        <v>3.805682432556395</v>
       </c>
       <c r="U78">
         <v>0.0553</v>
@@ -7831,7 +7831,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>4.799425384213357</v>
+        <v>4.737095184418379</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7839,22 +7839,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.102623266471295</v>
+        <v>0.1023937826741702</v>
       </c>
       <c r="C79">
-        <v>938.186210858343</v>
+        <v>917.086570257743</v>
       </c>
       <c r="D79">
-        <v>2609.501210858343</v>
+        <v>2614.596570257743</v>
       </c>
       <c r="E79">
-        <v>1951.715</v>
+        <v>1977.91</v>
       </c>
       <c r="F79">
-        <v>2017.015</v>
+        <v>2043.21</v>
       </c>
       <c r="G79">
         <v>345.7</v>
@@ -7875,28 +7875,28 @@
         <v>528.38</v>
       </c>
       <c r="M79">
-        <v>111.5409295</v>
+        <v>112.989513</v>
       </c>
       <c r="N79">
-        <v>416.8390705</v>
+        <v>415.390487</v>
       </c>
       <c r="O79">
-        <v>104.209767625</v>
+        <v>103.84762175</v>
       </c>
       <c r="P79">
-        <v>312.629302875</v>
+        <v>311.54286525</v>
       </c>
       <c r="Q79">
-        <v>313.749302875</v>
+        <v>312.66286525</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3073370281360653</v>
+        <v>0.3183785576098648</v>
       </c>
       <c r="T79">
-        <v>3.805682432556395</v>
+        <v>3.966350140094661</v>
       </c>
       <c r="U79">
         <v>0.0553</v>
@@ -7913,7 +7913,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>4.737095184418379</v>
+        <v>4.676363194874554</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7921,22 +7921,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1023937826741702</v>
+        <v>0.1021642988770455</v>
       </c>
       <c r="C80">
-        <v>917.086570257743</v>
+        <v>896.0068671698718</v>
       </c>
       <c r="D80">
-        <v>2614.596570257743</v>
+        <v>2619.711867169872</v>
       </c>
       <c r="E80">
-        <v>1977.91</v>
+        <v>2004.105</v>
       </c>
       <c r="F80">
-        <v>2043.21</v>
+        <v>2069.405</v>
       </c>
       <c r="G80">
         <v>345.7</v>
@@ -7957,28 +7957,28 @@
         <v>528.38</v>
       </c>
       <c r="M80">
-        <v>112.989513</v>
+        <v>114.4380965</v>
       </c>
       <c r="N80">
-        <v>415.390487</v>
+        <v>413.9419035</v>
       </c>
       <c r="O80">
-        <v>103.84762175</v>
+        <v>103.485475875</v>
       </c>
       <c r="P80">
-        <v>311.54286525</v>
+        <v>310.4564276249999</v>
       </c>
       <c r="Q80">
-        <v>312.66286525</v>
+        <v>311.576427625</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3183785576098648</v>
+        <v>0.3304716613192643</v>
       </c>
       <c r="T80">
-        <v>3.966350140094661</v>
+        <v>4.142319534065143</v>
       </c>
       <c r="U80">
         <v>0.0553</v>
@@ -7995,7 +7995,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>4.676363194874554</v>
+        <v>4.617168724053357</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8003,22 +8003,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1021642988770455</v>
+        <v>0.1019348150799207</v>
       </c>
       <c r="C81">
-        <v>896.0068671698718</v>
+        <v>874.9472188436639</v>
       </c>
       <c r="D81">
-        <v>2619.711867169872</v>
+        <v>2624.847218843664</v>
       </c>
       <c r="E81">
-        <v>2004.105</v>
+        <v>2030.3</v>
       </c>
       <c r="F81">
-        <v>2069.405</v>
+        <v>2095.6</v>
       </c>
       <c r="G81">
         <v>345.7</v>
@@ -8039,28 +8039,28 @@
         <v>528.38</v>
       </c>
       <c r="M81">
-        <v>114.4380965</v>
+        <v>115.88668</v>
       </c>
       <c r="N81">
-        <v>413.9419035</v>
+        <v>412.49332</v>
       </c>
       <c r="O81">
-        <v>103.485475875</v>
+        <v>103.12333</v>
       </c>
       <c r="P81">
-        <v>310.4564276249999</v>
+        <v>309.36999</v>
       </c>
       <c r="Q81">
-        <v>311.576427625</v>
+        <v>310.48999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3304716613192643</v>
+        <v>0.3437740753996038</v>
       </c>
       <c r="T81">
-        <v>4.142319534065143</v>
+        <v>4.335885867432673</v>
       </c>
       <c r="U81">
         <v>0.0553</v>
@@ -8077,7 +8077,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>4.617168724053357</v>
+        <v>4.559454115002691</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8085,22 +8085,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1019348150799207</v>
+        <v>0.101705331282796</v>
       </c>
       <c r="C82">
-        <v>874.9472188436639</v>
+        <v>853.9077434492151</v>
       </c>
       <c r="D82">
-        <v>2624.847218843664</v>
+        <v>2630.002743449215</v>
       </c>
       <c r="E82">
-        <v>2030.3</v>
+        <v>2056.495</v>
       </c>
       <c r="F82">
-        <v>2095.6</v>
+        <v>2121.795</v>
       </c>
       <c r="G82">
         <v>345.7</v>
@@ -8121,28 +8121,28 @@
         <v>528.38</v>
       </c>
       <c r="M82">
-        <v>115.88668</v>
+        <v>117.3352635</v>
       </c>
       <c r="N82">
-        <v>412.49332</v>
+        <v>411.0447365</v>
       </c>
       <c r="O82">
-        <v>103.12333</v>
+        <v>102.761184125</v>
       </c>
       <c r="P82">
-        <v>309.36999</v>
+        <v>308.283552375</v>
       </c>
       <c r="Q82">
-        <v>310.48999</v>
+        <v>309.403552375</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3437740753996038</v>
+        <v>0.3584767435936632</v>
       </c>
       <c r="T82">
-        <v>4.335885867432673</v>
+        <v>4.549827604312576</v>
       </c>
       <c r="U82">
         <v>0.0553</v>
@@ -8159,7 +8159,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>4.559454115002691</v>
+        <v>4.503164558027349</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8167,22 +8167,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.101705331282796</v>
+        <v>0.1030133474856712</v>
       </c>
       <c r="C83">
-        <v>853.9077434492151</v>
+        <v>798.5954399123361</v>
       </c>
       <c r="D83">
-        <v>2630.002743449215</v>
+        <v>2600.885439912337</v>
       </c>
       <c r="E83">
-        <v>2056.495</v>
+        <v>2082.69</v>
       </c>
       <c r="F83">
-        <v>2121.795</v>
+        <v>2147.99</v>
       </c>
       <c r="G83">
         <v>345.7</v>
@@ -8203,45 +8203,45 @@
         <v>528.38</v>
       </c>
       <c r="M83">
-        <v>117.3352635</v>
+        <v>124.153822</v>
       </c>
       <c r="N83">
-        <v>411.0447365</v>
+        <v>404.226178</v>
       </c>
       <c r="O83">
-        <v>102.761184125</v>
+        <v>101.0565445</v>
       </c>
       <c r="P83">
-        <v>308.283552375</v>
+        <v>303.1696335</v>
       </c>
       <c r="Q83">
-        <v>309.403552375</v>
+        <v>304.2896335</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3584767435936632</v>
+        <v>0.3748130415870626</v>
       </c>
       <c r="T83">
-        <v>4.549827604312576</v>
+        <v>4.787540645290244</v>
       </c>
       <c r="U83">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V83">
         <v>0.25</v>
       </c>
       <c r="W83">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y83">
-        <v>4.503164558027349</v>
+        <v>4.255849650766288</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8249,22 +8249,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1030133474856712</v>
+        <v>0.1028026136885465</v>
       </c>
       <c r="C84">
-        <v>798.5954399123361</v>
+        <v>777.04786691463</v>
       </c>
       <c r="D84">
-        <v>2600.885439912337</v>
+        <v>2605.532866914631</v>
       </c>
       <c r="E84">
-        <v>2082.69</v>
+        <v>2108.885</v>
       </c>
       <c r="F84">
-        <v>2147.99</v>
+        <v>2174.185</v>
       </c>
       <c r="G84">
         <v>345.7</v>
@@ -8285,28 +8285,28 @@
         <v>528.38</v>
       </c>
       <c r="M84">
-        <v>124.153822</v>
+        <v>125.667893</v>
       </c>
       <c r="N84">
-        <v>404.226178</v>
+        <v>402.7121069999999</v>
       </c>
       <c r="O84">
-        <v>101.0565445</v>
+        <v>100.67802675</v>
       </c>
       <c r="P84">
-        <v>303.1696335</v>
+        <v>302.03408025</v>
       </c>
       <c r="Q84">
-        <v>304.2896335</v>
+        <v>303.15408025</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3748130415870626</v>
+        <v>0.3930712569914501</v>
       </c>
       <c r="T84">
-        <v>4.787540645290244</v>
+        <v>5.053219926382933</v>
       </c>
       <c r="U84">
         <v>0.0578</v>
@@ -8323,7 +8323,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>4.255849650766288</v>
+        <v>4.204574353769104</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8331,22 +8331,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1028026136885465</v>
+        <v>0.1025918798914218</v>
       </c>
       <c r="C85">
-        <v>777.04786691463</v>
+        <v>755.5169322818479</v>
       </c>
       <c r="D85">
-        <v>2605.532866914631</v>
+        <v>2610.196932281848</v>
       </c>
       <c r="E85">
-        <v>2108.885</v>
+        <v>2135.08</v>
       </c>
       <c r="F85">
-        <v>2174.185</v>
+        <v>2200.38</v>
       </c>
       <c r="G85">
         <v>345.7</v>
@@ -8367,28 +8367,28 @@
         <v>528.38</v>
       </c>
       <c r="M85">
-        <v>125.667893</v>
+        <v>127.181964</v>
       </c>
       <c r="N85">
-        <v>402.7121069999999</v>
+        <v>401.198036</v>
       </c>
       <c r="O85">
-        <v>100.67802675</v>
+        <v>100.299509</v>
       </c>
       <c r="P85">
-        <v>302.03408025</v>
+        <v>300.898527</v>
       </c>
       <c r="Q85">
-        <v>303.15408025</v>
+        <v>302.018527</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3930712569914501</v>
+        <v>0.4136117493213861</v>
       </c>
       <c r="T85">
-        <v>5.053219926382933</v>
+        <v>5.352109117612208</v>
       </c>
       <c r="U85">
         <v>0.0578</v>
@@ -8405,7 +8405,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>4.204574353769104</v>
+        <v>4.154519897176614</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8413,22 +8413,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1025918798914217</v>
+        <v>0.102381146094297</v>
       </c>
       <c r="C86">
-        <v>755.5169322818479</v>
+        <v>734.0027255253322</v>
       </c>
       <c r="D86">
-        <v>2610.196932281848</v>
+        <v>2614.877725525332</v>
       </c>
       <c r="E86">
-        <v>2135.08</v>
+        <v>2161.275</v>
       </c>
       <c r="F86">
-        <v>2200.38</v>
+        <v>2226.575</v>
       </c>
       <c r="G86">
         <v>345.7</v>
@@ -8449,28 +8449,28 @@
         <v>528.38</v>
       </c>
       <c r="M86">
-        <v>127.181964</v>
+        <v>128.696035</v>
       </c>
       <c r="N86">
-        <v>401.198036</v>
+        <v>399.683965</v>
       </c>
       <c r="O86">
-        <v>100.299509</v>
+        <v>99.92099125</v>
       </c>
       <c r="P86">
-        <v>300.898527</v>
+        <v>299.76297375</v>
       </c>
       <c r="Q86">
-        <v>302.018527</v>
+        <v>300.88297375</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4136117493213858</v>
+        <v>0.4368909739619799</v>
       </c>
       <c r="T86">
-        <v>5.352109117612204</v>
+        <v>5.690850201005382</v>
       </c>
       <c r="U86">
         <v>0.0578</v>
@@ -8487,7 +8487,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>4.154519897176614</v>
+        <v>4.105643192503949</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8495,22 +8495,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.102381146094297</v>
+        <v>0.1021704122971722</v>
       </c>
       <c r="C87">
-        <v>734.0027255253322</v>
+        <v>712.5053367996543</v>
       </c>
       <c r="D87">
-        <v>2614.877725525332</v>
+        <v>2619.575336799654</v>
       </c>
       <c r="E87">
-        <v>2161.275</v>
+        <v>2187.47</v>
       </c>
       <c r="F87">
-        <v>2226.575</v>
+        <v>2252.77</v>
       </c>
       <c r="G87">
         <v>345.7</v>
@@ -8531,28 +8531,28 @@
         <v>528.38</v>
       </c>
       <c r="M87">
-        <v>128.696035</v>
+        <v>130.210106</v>
       </c>
       <c r="N87">
-        <v>399.683965</v>
+        <v>398.169894</v>
       </c>
       <c r="O87">
-        <v>99.92099125</v>
+        <v>99.5424735</v>
       </c>
       <c r="P87">
-        <v>299.76297375</v>
+        <v>298.6274205</v>
       </c>
       <c r="Q87">
-        <v>300.88297375</v>
+        <v>299.7474205</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4368909739619799</v>
+        <v>0.4634958021226588</v>
       </c>
       <c r="T87">
-        <v>5.690850201005382</v>
+        <v>6.077982867740443</v>
       </c>
       <c r="U87">
         <v>0.0578</v>
@@ -8569,7 +8569,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>4.105643192503949</v>
+        <v>4.05790315538181</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8577,22 +8577,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1021704122971722</v>
+        <v>0.1019596785000475</v>
       </c>
       <c r="C88">
-        <v>712.5053367996543</v>
+        <v>691.0248569084019</v>
       </c>
       <c r="D88">
-        <v>2619.575336799654</v>
+        <v>2624.289856908402</v>
       </c>
       <c r="E88">
-        <v>2187.47</v>
+        <v>2213.665</v>
       </c>
       <c r="F88">
-        <v>2252.77</v>
+        <v>2278.965</v>
       </c>
       <c r="G88">
         <v>345.7</v>
@@ -8613,28 +8613,28 @@
         <v>528.38</v>
       </c>
       <c r="M88">
-        <v>130.210106</v>
+        <v>131.724177</v>
       </c>
       <c r="N88">
-        <v>398.169894</v>
+        <v>396.6558229999999</v>
       </c>
       <c r="O88">
-        <v>99.5424735</v>
+        <v>99.16395574999999</v>
       </c>
       <c r="P88">
-        <v>298.6274205</v>
+        <v>297.4918672499999</v>
       </c>
       <c r="Q88">
-        <v>299.7474205</v>
+        <v>298.6118672499999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4634958021226588</v>
+        <v>0.4941936807695959</v>
       </c>
       <c r="T88">
-        <v>6.077982867740443</v>
+        <v>6.524674406280895</v>
       </c>
       <c r="U88">
         <v>0.0578</v>
@@ -8651,7 +8651,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>4.05790315538181</v>
+        <v>4.011260590377421</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8659,22 +8659,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1019596785000475</v>
+        <v>0.1040589447029227</v>
       </c>
       <c r="C89">
-        <v>691.0248569084019</v>
+        <v>618.6093696142839</v>
       </c>
       <c r="D89">
-        <v>2624.289856908402</v>
+        <v>2578.069369614284</v>
       </c>
       <c r="E89">
-        <v>2213.665</v>
+        <v>2239.86</v>
       </c>
       <c r="F89">
-        <v>2278.965</v>
+        <v>2305.16</v>
       </c>
       <c r="G89">
         <v>345.7</v>
@@ -8695,45 +8695,45 @@
         <v>528.38</v>
       </c>
       <c r="M89">
-        <v>131.724177</v>
+        <v>141.306308</v>
       </c>
       <c r="N89">
-        <v>396.6558229999999</v>
+        <v>387.073692</v>
       </c>
       <c r="O89">
-        <v>99.16395574999999</v>
+        <v>96.768423</v>
       </c>
       <c r="P89">
-        <v>297.4918672499999</v>
+        <v>290.305269</v>
       </c>
       <c r="Q89">
-        <v>298.6118672499999</v>
+        <v>291.425269</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4941936807695959</v>
+        <v>0.530007872524356</v>
       </c>
       <c r="T89">
-        <v>6.524674406280895</v>
+        <v>7.045814534578093</v>
       </c>
       <c r="U89">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V89">
         <v>0.25</v>
       </c>
       <c r="W89">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y89">
-        <v>4.011260590377421</v>
+        <v>3.739252744470544</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8741,22 +8741,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1040589447029227</v>
+        <v>0.103874460905798</v>
       </c>
       <c r="C90">
-        <v>618.6093696142839</v>
+        <v>596.410878211243</v>
       </c>
       <c r="D90">
-        <v>2578.069369614284</v>
+        <v>2582.065878211243</v>
       </c>
       <c r="E90">
-        <v>2239.86</v>
+        <v>2266.055</v>
       </c>
       <c r="F90">
-        <v>2305.16</v>
+        <v>2331.355</v>
       </c>
       <c r="G90">
         <v>345.7</v>
@@ -8777,28 +8777,28 @@
         <v>528.38</v>
       </c>
       <c r="M90">
-        <v>141.306308</v>
+        <v>142.9120615</v>
       </c>
       <c r="N90">
-        <v>387.073692</v>
+        <v>385.4679385</v>
       </c>
       <c r="O90">
-        <v>96.768423</v>
+        <v>96.366984625</v>
       </c>
       <c r="P90">
-        <v>290.305269</v>
+        <v>289.100953875</v>
       </c>
       <c r="Q90">
-        <v>291.425269</v>
+        <v>290.220953875</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.530007872524356</v>
+        <v>0.5723337355072543</v>
       </c>
       <c r="T90">
-        <v>7.045814534578093</v>
+        <v>7.66170741347478</v>
       </c>
       <c r="U90">
         <v>0.0613</v>
@@ -8815,7 +8815,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>3.739252744470544</v>
+        <v>3.697238668689976</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8823,22 +8823,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.103874460905798</v>
+        <v>0.1036899771086732</v>
       </c>
       <c r="C91">
-        <v>596.410878211243</v>
+        <v>574.2247967762401</v>
       </c>
       <c r="D91">
-        <v>2582.065878211243</v>
+        <v>2586.07479677624</v>
       </c>
       <c r="E91">
-        <v>2266.055</v>
+        <v>2292.25</v>
       </c>
       <c r="F91">
-        <v>2331.355</v>
+        <v>2357.55</v>
       </c>
       <c r="G91">
         <v>345.7</v>
@@ -8859,28 +8859,28 @@
         <v>528.38</v>
       </c>
       <c r="M91">
-        <v>142.9120615</v>
+        <v>144.517815</v>
       </c>
       <c r="N91">
-        <v>385.4679385</v>
+        <v>383.862185</v>
       </c>
       <c r="O91">
-        <v>96.366984625</v>
+        <v>95.96554624999999</v>
       </c>
       <c r="P91">
-        <v>289.100953875</v>
+        <v>287.89663875</v>
       </c>
       <c r="Q91">
-        <v>290.220953875</v>
+        <v>289.01663875</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5723337355072543</v>
+        <v>0.6231247710867324</v>
       </c>
       <c r="T91">
-        <v>7.66170741347478</v>
+        <v>8.400778868150805</v>
       </c>
       <c r="U91">
         <v>0.0613</v>
@@ -8897,7 +8897,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>3.697238668689976</v>
+        <v>3.656158239037865</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8905,22 +8905,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1036899771086732</v>
+        <v>0.1035054933115485</v>
       </c>
       <c r="C92">
-        <v>574.2247967762401</v>
+        <v>552.051183202354</v>
       </c>
       <c r="D92">
-        <v>2586.07479677624</v>
+        <v>2590.096183202354</v>
       </c>
       <c r="E92">
-        <v>2292.25</v>
+        <v>2318.445</v>
       </c>
       <c r="F92">
-        <v>2357.55</v>
+        <v>2383.745</v>
       </c>
       <c r="G92">
         <v>345.7</v>
@@ -8941,28 +8941,28 @@
         <v>528.38</v>
       </c>
       <c r="M92">
-        <v>144.517815</v>
+        <v>146.1235685</v>
       </c>
       <c r="N92">
-        <v>383.862185</v>
+        <v>382.2564315</v>
       </c>
       <c r="O92">
-        <v>95.96554624999999</v>
+        <v>95.56410787499999</v>
       </c>
       <c r="P92">
-        <v>287.89663875</v>
+        <v>286.692323625</v>
       </c>
       <c r="Q92">
-        <v>289.01663875</v>
+        <v>287.812323625</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6231247710867324</v>
+        <v>0.6852027034616498</v>
       </c>
       <c r="T92">
-        <v>8.400778868150805</v>
+        <v>9.304088423865945</v>
       </c>
       <c r="U92">
         <v>0.0613</v>
@@ -8979,7 +8979,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>3.656158239037865</v>
+        <v>3.615980675971515</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8987,22 +8987,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1035054933115485</v>
+        <v>0.1033210095144237</v>
       </c>
       <c r="C93">
-        <v>552.051183202354</v>
+        <v>529.8900957433207</v>
       </c>
       <c r="D93">
-        <v>2590.096183202354</v>
+        <v>2594.130095743321</v>
       </c>
       <c r="E93">
-        <v>2318.445</v>
+        <v>2344.64</v>
       </c>
       <c r="F93">
-        <v>2383.745</v>
+        <v>2409.94</v>
       </c>
       <c r="G93">
         <v>345.7</v>
@@ -9023,28 +9023,28 @@
         <v>528.38</v>
       </c>
       <c r="M93">
-        <v>146.1235685</v>
+        <v>147.729322</v>
       </c>
       <c r="N93">
-        <v>382.2564315</v>
+        <v>380.650678</v>
       </c>
       <c r="O93">
-        <v>95.56410787499999</v>
+        <v>95.16266949999999</v>
       </c>
       <c r="P93">
-        <v>286.692323625</v>
+        <v>285.4880085</v>
       </c>
       <c r="Q93">
-        <v>287.812323625</v>
+        <v>286.6080085</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6852027034616498</v>
+        <v>0.7628001189302968</v>
       </c>
       <c r="T93">
-        <v>9.304088423865945</v>
+        <v>10.43322536850987</v>
       </c>
       <c r="U93">
         <v>0.0613</v>
@@ -9061,7 +9061,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>3.615980675971515</v>
+        <v>3.576676538189216</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9069,22 +9069,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1033210095144237</v>
+        <v>0.103136525717299</v>
       </c>
       <c r="C94">
-        <v>529.8900957433207</v>
+        <v>507.7415930163506</v>
       </c>
       <c r="D94">
-        <v>2594.130095743321</v>
+        <v>2598.176593016351</v>
       </c>
       <c r="E94">
-        <v>2344.64</v>
+        <v>2370.835</v>
       </c>
       <c r="F94">
-        <v>2409.94</v>
+        <v>2436.135</v>
       </c>
       <c r="G94">
         <v>345.7</v>
@@ -9105,28 +9105,28 @@
         <v>528.38</v>
       </c>
       <c r="M94">
-        <v>147.729322</v>
+        <v>149.3350755</v>
       </c>
       <c r="N94">
-        <v>380.650678</v>
+        <v>379.0449245</v>
       </c>
       <c r="O94">
-        <v>95.16266949999999</v>
+        <v>94.76123112499999</v>
       </c>
       <c r="P94">
-        <v>285.4880085</v>
+        <v>284.283693375</v>
       </c>
       <c r="Q94">
-        <v>286.6080085</v>
+        <v>285.403693375</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7628001189302968</v>
+        <v>0.862568224532843</v>
       </c>
       <c r="T94">
-        <v>10.43322536850987</v>
+        <v>11.88497286876635</v>
       </c>
       <c r="U94">
         <v>0.0613</v>
@@ -9143,7 +9143,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>3.576676538189216</v>
+        <v>3.538217650681805</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9151,22 +9151,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.103136525717299</v>
+        <v>0.1029520419201742</v>
       </c>
       <c r="C95">
-        <v>507.7415930163506</v>
+        <v>485.6057340049674</v>
       </c>
       <c r="D95">
-        <v>2598.176593016351</v>
+        <v>2602.235734004968</v>
       </c>
       <c r="E95">
-        <v>2370.835</v>
+        <v>2397.03</v>
       </c>
       <c r="F95">
-        <v>2436.135</v>
+        <v>2462.33</v>
       </c>
       <c r="G95">
         <v>345.7</v>
@@ -9187,28 +9187,28 @@
         <v>528.38</v>
       </c>
       <c r="M95">
-        <v>149.3350755</v>
+        <v>150.940829</v>
       </c>
       <c r="N95">
-        <v>379.0449245</v>
+        <v>377.439171</v>
       </c>
       <c r="O95">
-        <v>94.76123112499999</v>
+        <v>94.35979275</v>
       </c>
       <c r="P95">
-        <v>284.283693375</v>
+        <v>283.07937825</v>
       </c>
       <c r="Q95">
-        <v>285.403693375</v>
+        <v>284.19937825</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.862568224532843</v>
+        <v>0.9955923653362376</v>
       </c>
       <c r="T95">
-        <v>11.88497286876635</v>
+        <v>13.82063620244165</v>
       </c>
       <c r="U95">
         <v>0.0613</v>
@@ -9225,7 +9225,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>3.538217650681805</v>
+        <v>3.500577037376679</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9233,22 +9233,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1029520419201742</v>
+        <v>0.1047625581230495</v>
       </c>
       <c r="C96">
-        <v>485.6057340049674</v>
+        <v>420.1147601841321</v>
       </c>
       <c r="D96">
-        <v>2602.235734004968</v>
+        <v>2562.939760184132</v>
       </c>
       <c r="E96">
-        <v>2397.03</v>
+        <v>2423.225</v>
       </c>
       <c r="F96">
-        <v>2462.33</v>
+        <v>2488.525</v>
       </c>
       <c r="G96">
         <v>345.7</v>
@@ -9269,45 +9269,45 @@
         <v>528.38</v>
       </c>
       <c r="M96">
-        <v>150.940829</v>
+        <v>159.5144525</v>
       </c>
       <c r="N96">
-        <v>377.439171</v>
+        <v>368.8655475</v>
       </c>
       <c r="O96">
-        <v>94.35979275</v>
+        <v>92.216386875</v>
       </c>
       <c r="P96">
-        <v>283.07937825</v>
+        <v>276.649160625</v>
       </c>
       <c r="Q96">
-        <v>284.19937825</v>
+        <v>277.769160625</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9955923653362376</v>
+        <v>1.181826162460991</v>
       </c>
       <c r="T96">
-        <v>13.82063620244165</v>
+        <v>16.53056486958709</v>
       </c>
       <c r="U96">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V96">
         <v>0.25</v>
       </c>
       <c r="W96">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y96">
-        <v>3.500577037376679</v>
+        <v>3.312427129447722</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9315,22 +9315,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1047625581230495</v>
+        <v>0.1045990743259247</v>
       </c>
       <c r="C97">
-        <v>420.1147601841321</v>
+        <v>397.4192497939734</v>
       </c>
       <c r="D97">
-        <v>2562.939760184132</v>
+        <v>2566.439249793974</v>
       </c>
       <c r="E97">
-        <v>2423.225</v>
+        <v>2449.42</v>
       </c>
       <c r="F97">
-        <v>2488.525</v>
+        <v>2514.72</v>
       </c>
       <c r="G97">
         <v>345.7</v>
@@ -9351,28 +9351,28 @@
         <v>528.38</v>
       </c>
       <c r="M97">
-        <v>159.5144525</v>
+        <v>161.193552</v>
       </c>
       <c r="N97">
-        <v>368.8655475</v>
+        <v>367.1864479999999</v>
       </c>
       <c r="O97">
-        <v>92.216386875</v>
+        <v>91.79661199999998</v>
       </c>
       <c r="P97">
-        <v>276.649160625</v>
+        <v>275.3898359999999</v>
       </c>
       <c r="Q97">
-        <v>277.769160625</v>
+        <v>276.509836</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.181826162460991</v>
+        <v>1.46117685814812</v>
       </c>
       <c r="T97">
-        <v>16.53056486958709</v>
+        <v>20.59545787030523</v>
       </c>
       <c r="U97">
         <v>0.0641</v>
@@ -9389,7 +9389,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>3.312427129447722</v>
+        <v>3.277922680182641</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9397,22 +9397,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1045990743259247</v>
+        <v>0.1044355905288</v>
       </c>
       <c r="C98">
-        <v>397.4192497939739</v>
+        <v>374.7333090176639</v>
       </c>
       <c r="D98">
-        <v>2566.439249793974</v>
+        <v>2569.948309017664</v>
       </c>
       <c r="E98">
-        <v>2449.42</v>
+        <v>2475.615</v>
       </c>
       <c r="F98">
-        <v>2514.72</v>
+        <v>2540.915</v>
       </c>
       <c r="G98">
         <v>345.7</v>
@@ -9433,28 +9433,28 @@
         <v>528.38</v>
       </c>
       <c r="M98">
-        <v>161.193552</v>
+        <v>162.8726515</v>
       </c>
       <c r="N98">
-        <v>367.186448</v>
+        <v>365.5073485</v>
       </c>
       <c r="O98">
-        <v>91.796612</v>
+        <v>91.37683712499999</v>
       </c>
       <c r="P98">
-        <v>275.389836</v>
+        <v>274.130511375</v>
       </c>
       <c r="Q98">
-        <v>276.509836</v>
+        <v>275.250511375</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.461176858148117</v>
+        <v>1.926761350959997</v>
       </c>
       <c r="T98">
-        <v>20.59545787030518</v>
+        <v>27.37027953816872</v>
       </c>
       <c r="U98">
         <v>0.0641</v>
@@ -9471,7 +9471,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>3.277922680182641</v>
+        <v>3.24412966286117</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9479,22 +9479,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1044355905288</v>
+        <v>0.1042721067316752</v>
       </c>
       <c r="C99">
-        <v>374.7333090176639</v>
+        <v>352.0569771621758</v>
       </c>
       <c r="D99">
-        <v>2569.948309017664</v>
+        <v>2573.466977162176</v>
       </c>
       <c r="E99">
-        <v>2475.615</v>
+        <v>2501.81</v>
       </c>
       <c r="F99">
-        <v>2540.915</v>
+        <v>2567.11</v>
       </c>
       <c r="G99">
         <v>345.7</v>
@@ -9515,28 +9515,28 @@
         <v>528.38</v>
       </c>
       <c r="M99">
-        <v>162.8726515</v>
+        <v>164.551751</v>
       </c>
       <c r="N99">
-        <v>365.5073485</v>
+        <v>363.828249</v>
       </c>
       <c r="O99">
-        <v>91.37683712499999</v>
+        <v>90.95706224999999</v>
       </c>
       <c r="P99">
-        <v>274.130511375</v>
+        <v>272.87118675</v>
       </c>
       <c r="Q99">
-        <v>275.250511375</v>
+        <v>273.99118675</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.926761350959997</v>
+        <v>2.857930336583758</v>
       </c>
       <c r="T99">
-        <v>27.37027953816872</v>
+        <v>40.91992287389581</v>
       </c>
       <c r="U99">
         <v>0.0641</v>
@@ -9553,7 +9553,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>3.24412966286117</v>
+        <v>3.211026298954424</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9561,22 +9561,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1042721067316752</v>
+        <v>0.1041086229345505</v>
       </c>
       <c r="C100">
-        <v>352.0569771621758</v>
+        <v>329.3902937500447</v>
       </c>
       <c r="D100">
-        <v>2573.466977162176</v>
+        <v>2576.995293750045</v>
       </c>
       <c r="E100">
-        <v>2501.81</v>
+        <v>2528.005</v>
       </c>
       <c r="F100">
-        <v>2567.11</v>
+        <v>2593.305</v>
       </c>
       <c r="G100">
         <v>345.7</v>
@@ -9597,28 +9597,28 @@
         <v>528.38</v>
       </c>
       <c r="M100">
-        <v>164.551751</v>
+        <v>166.2308505</v>
       </c>
       <c r="N100">
-        <v>363.828249</v>
+        <v>362.1491495</v>
       </c>
       <c r="O100">
-        <v>90.95706224999999</v>
+        <v>90.53728737500001</v>
       </c>
       <c r="P100">
-        <v>272.87118675</v>
+        <v>271.611862125</v>
       </c>
       <c r="Q100">
-        <v>273.99118675</v>
+        <v>272.731862125</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.857930336583758</v>
+        <v>5.651437293455041</v>
       </c>
       <c r="T100">
-        <v>40.91992287389581</v>
+        <v>81.56885288107709</v>
       </c>
       <c r="U100">
         <v>0.0641</v>
@@ -9635,91 +9635,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>3.211026298954424</v>
+        <v>3.178591689874077</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1041086229345505</v>
-      </c>
-      <c r="C101">
-        <v>329.3902937500447</v>
-      </c>
-      <c r="D101">
-        <v>2576.995293750045</v>
-      </c>
-      <c r="E101">
-        <v>2528.005</v>
-      </c>
-      <c r="F101">
-        <v>2593.305</v>
-      </c>
-      <c r="G101">
-        <v>345.7</v>
-      </c>
-      <c r="H101">
-        <v>2554.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>529.5</v>
-      </c>
-      <c r="K101">
-        <v>1.12</v>
-      </c>
-      <c r="L101">
-        <v>528.38</v>
-      </c>
-      <c r="M101">
-        <v>166.2308505</v>
-      </c>
-      <c r="N101">
-        <v>362.1491495</v>
-      </c>
-      <c r="O101">
-        <v>90.53728737500001</v>
-      </c>
-      <c r="P101">
-        <v>271.611862125</v>
-      </c>
-      <c r="Q101">
-        <v>272.731862125</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.651437293455041</v>
-      </c>
-      <c r="T101">
-        <v>81.56885288107709</v>
-      </c>
-      <c r="U101">
-        <v>0.0641</v>
-      </c>
-      <c r="V101">
-        <v>0.25</v>
-      </c>
-      <c r="W101">
-        <v>0.04807500000000001</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ba2/BB</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>3.178591689874077</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
